--- a/unit13_protocall.bus.controller_driver/unit13_protocall.bus.controller_driver.xlsx
+++ b/unit13_protocall.bus.controller_driver/unit13_protocall.bus.controller_driver.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E4FFA1-BB3D-4BFA-8944-28AC6279DF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685500D7-F8C4-4EDF-90B2-F239BAE99963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Các loại driver" sheetId="3" r:id="rId1"/>
     <sheet name="Các hàm đăng ký" sheetId="1" r:id="rId2"/>
     <sheet name="Controller_driver share API" sheetId="4" r:id="rId3"/>
-    <sheet name="viết protocal driver" sheetId="2" r:id="rId4"/>
+    <sheet name="protocal_driver" sheetId="2" r:id="rId4"/>
+    <sheet name="debug controller driver" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3034,7 +3035,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3078,87 +3079,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3169,8 +3089,8 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
@@ -3185,27 +3105,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3222,8 +3130,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3264,7 +3170,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -3292,6 +3198,99 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4165,9 +4164,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0B779B-AFA3-4878-AA00-035278DBEE3E}">
   <dimension ref="A1:CD71"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:82" ht="14.4" thickBot="1"/>
+    <row r="1" spans="1:82" ht="15" thickBot="1"/>
     <row r="2" spans="1:82">
       <c r="B2" s="2" t="s">
         <v>16</v>
@@ -4191,7 +4190,7 @@
       <c r="S2" s="3"/>
       <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:82" ht="14.4" thickBot="1">
+    <row r="3" spans="1:82" ht="15.75" thickBot="1">
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
@@ -4214,7 +4213,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="7"/>
     </row>
-    <row r="4" spans="1:82">
+    <row r="4" spans="1:82" ht="15">
       <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
@@ -4236,47 +4235,47 @@
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
       <c r="T4" s="7"/>
-      <c r="X4" s="60" t="s">
+      <c r="X4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="Y4" s="61"/>
-      <c r="Z4" s="61"/>
-      <c r="AA4" s="61"/>
-      <c r="AB4" s="61"/>
-      <c r="AC4" s="61"/>
-      <c r="AD4" s="61"/>
-      <c r="AE4" s="61"/>
-      <c r="AF4" s="61"/>
-      <c r="AG4" s="61"/>
-      <c r="AH4" s="61"/>
-      <c r="AI4" s="61"/>
-      <c r="AJ4" s="61"/>
-      <c r="AK4" s="61"/>
-      <c r="AL4" s="61"/>
-      <c r="AM4" s="61"/>
-      <c r="AN4" s="61"/>
-      <c r="AO4" s="61"/>
-      <c r="AP4" s="61"/>
-      <c r="AQ4" s="61"/>
-      <c r="AR4" s="61"/>
-      <c r="AS4" s="61"/>
-      <c r="AT4" s="61"/>
-      <c r="AU4" s="61"/>
-      <c r="AV4" s="61"/>
-      <c r="AW4" s="61"/>
-      <c r="AX4" s="61"/>
-      <c r="AY4" s="61"/>
-      <c r="AZ4" s="61"/>
-      <c r="BA4" s="61"/>
-      <c r="BB4" s="61"/>
-      <c r="BC4" s="61"/>
-      <c r="BD4" s="61"/>
-      <c r="BE4" s="61"/>
-      <c r="BF4" s="61"/>
-      <c r="BG4" s="61"/>
-      <c r="BH4" s="62"/>
-    </row>
-    <row r="5" spans="1:82" ht="14.4" thickBot="1">
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="30"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="30"/>
+      <c r="AM4" s="30"/>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="30"/>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="30"/>
+      <c r="AS4" s="30"/>
+      <c r="AT4" s="30"/>
+      <c r="AU4" s="30"/>
+      <c r="AV4" s="30"/>
+      <c r="AW4" s="30"/>
+      <c r="AX4" s="30"/>
+      <c r="AY4" s="30"/>
+      <c r="AZ4" s="30"/>
+      <c r="BA4" s="30"/>
+      <c r="BB4" s="30"/>
+      <c r="BC4" s="30"/>
+      <c r="BD4" s="30"/>
+      <c r="BE4" s="30"/>
+      <c r="BF4" s="30"/>
+      <c r="BG4" s="30"/>
+      <c r="BH4" s="31"/>
+    </row>
+    <row r="5" spans="1:82" ht="15.75" thickBot="1">
       <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
@@ -4298,47 +4297,47 @@
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
       <c r="T5" s="7"/>
-      <c r="X5" s="63" t="s">
+      <c r="X5" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="Y5" s="64"/>
-      <c r="Z5" s="64"/>
-      <c r="AA5" s="64"/>
-      <c r="AB5" s="64"/>
-      <c r="AC5" s="64"/>
-      <c r="AD5" s="64"/>
-      <c r="AE5" s="64"/>
-      <c r="AF5" s="64"/>
-      <c r="AG5" s="64"/>
-      <c r="AH5" s="64"/>
-      <c r="AI5" s="64"/>
-      <c r="AJ5" s="64"/>
-      <c r="AK5" s="64"/>
-      <c r="AL5" s="64"/>
-      <c r="AM5" s="64"/>
-      <c r="AN5" s="64"/>
-      <c r="AO5" s="64"/>
-      <c r="AP5" s="64"/>
-      <c r="AQ5" s="64"/>
-      <c r="AR5" s="64"/>
-      <c r="AS5" s="64"/>
-      <c r="AT5" s="64"/>
-      <c r="AU5" s="64"/>
-      <c r="AV5" s="64"/>
-      <c r="AW5" s="64"/>
-      <c r="AX5" s="64"/>
-      <c r="AY5" s="64"/>
-      <c r="AZ5" s="64"/>
-      <c r="BA5" s="64"/>
-      <c r="BB5" s="64"/>
-      <c r="BC5" s="64"/>
-      <c r="BD5" s="64"/>
-      <c r="BE5" s="64"/>
-      <c r="BF5" s="64"/>
-      <c r="BG5" s="64"/>
-      <c r="BH5" s="65"/>
-    </row>
-    <row r="6" spans="1:82">
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="33"/>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="33"/>
+      <c r="AG5" s="33"/>
+      <c r="AH5" s="33"/>
+      <c r="AI5" s="33"/>
+      <c r="AJ5" s="33"/>
+      <c r="AK5" s="33"/>
+      <c r="AL5" s="33"/>
+      <c r="AM5" s="33"/>
+      <c r="AN5" s="33"/>
+      <c r="AO5" s="33"/>
+      <c r="AP5" s="33"/>
+      <c r="AQ5" s="33"/>
+      <c r="AR5" s="33"/>
+      <c r="AS5" s="33"/>
+      <c r="AT5" s="33"/>
+      <c r="AU5" s="33"/>
+      <c r="AV5" s="33"/>
+      <c r="AW5" s="33"/>
+      <c r="AX5" s="33"/>
+      <c r="AY5" s="33"/>
+      <c r="AZ5" s="33"/>
+      <c r="BA5" s="33"/>
+      <c r="BB5" s="33"/>
+      <c r="BC5" s="33"/>
+      <c r="BD5" s="33"/>
+      <c r="BE5" s="33"/>
+      <c r="BF5" s="33"/>
+      <c r="BG5" s="33"/>
+      <c r="BH5" s="34"/>
+    </row>
+    <row r="6" spans="1:82" ht="15">
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -4361,7 +4360,7 @@
       <c r="S6" s="6"/>
       <c r="T6" s="7"/>
     </row>
-    <row r="7" spans="1:82">
+    <row r="7" spans="1:82" ht="15">
       <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
@@ -4384,7 +4383,7 @@
       <c r="S7" s="6"/>
       <c r="T7" s="7"/>
     </row>
-    <row r="8" spans="1:82" ht="14.4" thickBot="1">
+    <row r="8" spans="1:82" ht="15.75" thickBot="1">
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
@@ -4407,601 +4406,599 @@
       <c r="S8" s="9"/>
       <c r="T8" s="10"/>
     </row>
-    <row r="9" spans="1:82" ht="14.4" thickBot="1"/>
-    <row r="10" spans="1:82" s="12" customFormat="1" ht="14.4" thickBot="1">
+    <row r="9" spans="1:82" ht="15" thickBot="1"/>
+    <row r="10" spans="1:82" s="12" customFormat="1" ht="15.75" thickBot="1">
       <c r="A10" s="11"/>
       <c r="C10" s="14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:82" ht="14.4" thickBot="1"/>
-    <row r="12" spans="1:82">
-      <c r="D12" s="54" t="s">
+    <row r="11" spans="1:82" ht="15" thickBot="1"/>
+    <row r="12" spans="1:82" ht="15">
+      <c r="D12" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44" t="s">
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
+      <c r="G12" s="108"/>
+      <c r="H12" s="108"/>
+      <c r="I12" s="108"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="44"/>
-      <c r="S12" s="44"/>
-      <c r="T12" s="44"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="44"/>
-      <c r="W12" s="44"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="44"/>
-      <c r="AE12" s="44"/>
-      <c r="AF12" s="44"/>
-      <c r="AG12" s="44"/>
-      <c r="AH12" s="44" t="s">
+      <c r="M12" s="108"/>
+      <c r="N12" s="108"/>
+      <c r="O12" s="108"/>
+      <c r="P12" s="108"/>
+      <c r="Q12" s="108"/>
+      <c r="R12" s="108"/>
+      <c r="S12" s="108"/>
+      <c r="T12" s="108"/>
+      <c r="U12" s="108"/>
+      <c r="V12" s="108"/>
+      <c r="W12" s="108"/>
+      <c r="X12" s="108"/>
+      <c r="Y12" s="108"/>
+      <c r="Z12" s="108"/>
+      <c r="AA12" s="108"/>
+      <c r="AB12" s="108"/>
+      <c r="AC12" s="108"/>
+      <c r="AD12" s="108"/>
+      <c r="AE12" s="108"/>
+      <c r="AF12" s="108"/>
+      <c r="AG12" s="108"/>
+      <c r="AH12" s="108" t="s">
         <v>208</v>
       </c>
-      <c r="AI12" s="44"/>
-      <c r="AJ12" s="44"/>
-      <c r="AK12" s="44"/>
-      <c r="AL12" s="44"/>
-      <c r="AM12" s="44"/>
-      <c r="AN12" s="44"/>
-      <c r="AO12" s="44"/>
-      <c r="AP12" s="44"/>
-      <c r="AQ12" s="44"/>
-      <c r="AR12" s="44"/>
-      <c r="AS12" s="44"/>
-      <c r="AT12" s="44"/>
-      <c r="AU12" s="44"/>
-      <c r="AV12" s="44"/>
-      <c r="AW12" s="44"/>
-      <c r="AX12" s="44"/>
-      <c r="AY12" s="44"/>
-      <c r="AZ12" s="55" t="s">
+      <c r="AI12" s="108"/>
+      <c r="AJ12" s="108"/>
+      <c r="AK12" s="108"/>
+      <c r="AL12" s="108"/>
+      <c r="AM12" s="108"/>
+      <c r="AN12" s="108"/>
+      <c r="AO12" s="108"/>
+      <c r="AP12" s="108"/>
+      <c r="AQ12" s="108"/>
+      <c r="AR12" s="108"/>
+      <c r="AS12" s="108"/>
+      <c r="AT12" s="108"/>
+      <c r="AU12" s="108"/>
+      <c r="AV12" s="108"/>
+      <c r="AW12" s="108"/>
+      <c r="AX12" s="108"/>
+      <c r="AY12" s="108"/>
+      <c r="AZ12" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="BA12" s="55"/>
-      <c r="BB12" s="55"/>
-      <c r="BC12" s="55"/>
-      <c r="BD12" s="55"/>
-      <c r="BE12" s="55"/>
-      <c r="BF12" s="55"/>
-      <c r="BG12" s="55"/>
-      <c r="BH12" s="55"/>
-      <c r="BI12" s="56"/>
-    </row>
-    <row r="13" spans="1:82" ht="29.4" customHeight="1">
-      <c r="D13" s="48" t="s">
+      <c r="BA12" s="121"/>
+      <c r="BB12" s="121"/>
+      <c r="BC12" s="121"/>
+      <c r="BD12" s="121"/>
+      <c r="BE12" s="121"/>
+      <c r="BF12" s="121"/>
+      <c r="BG12" s="121"/>
+      <c r="BH12" s="121"/>
+      <c r="BI12" s="122"/>
+    </row>
+    <row r="13" spans="1:82" ht="29.45" customHeight="1">
+      <c r="D13" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="39" t="s">
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="109" t="s">
         <v>205</v>
       </c>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
-      <c r="U13" s="39"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="39"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="39"/>
-      <c r="Z13" s="39"/>
-      <c r="AA13" s="39"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="39"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="39"/>
-      <c r="AF13" s="39"/>
-      <c r="AG13" s="39"/>
-      <c r="AH13" s="59" t="s">
+      <c r="M13" s="109"/>
+      <c r="N13" s="109"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="109"/>
+      <c r="S13" s="109"/>
+      <c r="T13" s="109"/>
+      <c r="U13" s="109"/>
+      <c r="V13" s="109"/>
+      <c r="W13" s="109"/>
+      <c r="X13" s="109"/>
+      <c r="Y13" s="109"/>
+      <c r="Z13" s="109"/>
+      <c r="AA13" s="109"/>
+      <c r="AB13" s="109"/>
+      <c r="AC13" s="109"/>
+      <c r="AD13" s="109"/>
+      <c r="AE13" s="109"/>
+      <c r="AF13" s="109"/>
+      <c r="AG13" s="109"/>
+      <c r="AH13" s="137" t="s">
         <v>210</v>
       </c>
-      <c r="AI13" s="59"/>
-      <c r="AJ13" s="59"/>
-      <c r="AK13" s="59"/>
-      <c r="AL13" s="59"/>
-      <c r="AM13" s="59"/>
-      <c r="AN13" s="59"/>
-      <c r="AO13" s="59"/>
-      <c r="AP13" s="59"/>
-      <c r="AQ13" s="59"/>
-      <c r="AR13" s="59"/>
-      <c r="AS13" s="59"/>
-      <c r="AT13" s="59"/>
-      <c r="AU13" s="59"/>
-      <c r="AV13" s="59"/>
-      <c r="AW13" s="59"/>
-      <c r="AX13" s="59"/>
-      <c r="AY13" s="59"/>
-      <c r="AZ13" s="88" t="s">
+      <c r="AI13" s="137"/>
+      <c r="AJ13" s="137"/>
+      <c r="AK13" s="137"/>
+      <c r="AL13" s="137"/>
+      <c r="AM13" s="137"/>
+      <c r="AN13" s="137"/>
+      <c r="AO13" s="137"/>
+      <c r="AP13" s="137"/>
+      <c r="AQ13" s="137"/>
+      <c r="AR13" s="137"/>
+      <c r="AS13" s="137"/>
+      <c r="AT13" s="137"/>
+      <c r="AU13" s="137"/>
+      <c r="AV13" s="137"/>
+      <c r="AW13" s="137"/>
+      <c r="AX13" s="137"/>
+      <c r="AY13" s="137"/>
+      <c r="AZ13" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="BA13" s="88"/>
-      <c r="BB13" s="88"/>
-      <c r="BC13" s="88"/>
-      <c r="BD13" s="88"/>
-      <c r="BE13" s="88"/>
-      <c r="BF13" s="88"/>
-      <c r="BG13" s="88"/>
-      <c r="BH13" s="88"/>
-      <c r="BI13" s="89"/>
-      <c r="BJ13" s="90" t="s">
+      <c r="BA13" s="123"/>
+      <c r="BB13" s="123"/>
+      <c r="BC13" s="123"/>
+      <c r="BD13" s="123"/>
+      <c r="BE13" s="123"/>
+      <c r="BF13" s="123"/>
+      <c r="BG13" s="123"/>
+      <c r="BH13" s="123"/>
+      <c r="BI13" s="124"/>
+      <c r="BJ13" s="57" t="s">
         <v>207</v>
       </c>
-      <c r="BK13" s="90"/>
-      <c r="BL13" s="90"/>
-      <c r="BM13" s="90"/>
-      <c r="BN13" s="90"/>
-      <c r="BO13" s="90"/>
-      <c r="BP13" s="90"/>
-      <c r="BQ13" s="90"/>
-      <c r="BR13" s="90"/>
-      <c r="BS13" s="90"/>
-      <c r="BT13" s="90"/>
-      <c r="BU13" s="90"/>
-      <c r="BV13" s="90"/>
-      <c r="BW13" s="90"/>
-      <c r="BX13" s="90"/>
-      <c r="BY13" s="90"/>
-      <c r="BZ13" s="90"/>
-      <c r="CA13" s="90"/>
-      <c r="CB13" s="90"/>
-      <c r="CC13" s="90"/>
-      <c r="CD13" s="90"/>
+      <c r="BK13" s="57"/>
+      <c r="BL13" s="57"/>
+      <c r="BM13" s="57"/>
+      <c r="BN13" s="57"/>
+      <c r="BO13" s="57"/>
+      <c r="BP13" s="57"/>
+      <c r="BQ13" s="57"/>
+      <c r="BR13" s="57"/>
+      <c r="BS13" s="57"/>
+      <c r="BT13" s="57"/>
+      <c r="BU13" s="57"/>
+      <c r="BV13" s="57"/>
+      <c r="BW13" s="57"/>
+      <c r="BX13" s="57"/>
+      <c r="BY13" s="57"/>
+      <c r="BZ13" s="57"/>
+      <c r="CA13" s="57"/>
+      <c r="CB13" s="57"/>
+      <c r="CC13" s="57"/>
+      <c r="CD13" s="57"/>
     </row>
     <row r="14" spans="1:82" ht="30" customHeight="1">
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="39" t="s">
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="109" t="s">
         <v>219</v>
       </c>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="39"/>
-      <c r="W14" s="39"/>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="39"/>
-      <c r="AA14" s="39"/>
-      <c r="AB14" s="39"/>
-      <c r="AC14" s="39"/>
-      <c r="AD14" s="39"/>
-      <c r="AE14" s="39"/>
-      <c r="AF14" s="39"/>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="59" t="s">
+      <c r="M14" s="109"/>
+      <c r="N14" s="109"/>
+      <c r="O14" s="109"/>
+      <c r="P14" s="109"/>
+      <c r="Q14" s="109"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="109"/>
+      <c r="T14" s="109"/>
+      <c r="U14" s="109"/>
+      <c r="V14" s="109"/>
+      <c r="W14" s="109"/>
+      <c r="X14" s="109"/>
+      <c r="Y14" s="109"/>
+      <c r="Z14" s="109"/>
+      <c r="AA14" s="109"/>
+      <c r="AB14" s="109"/>
+      <c r="AC14" s="109"/>
+      <c r="AD14" s="109"/>
+      <c r="AE14" s="109"/>
+      <c r="AF14" s="109"/>
+      <c r="AG14" s="109"/>
+      <c r="AH14" s="137" t="s">
         <v>209</v>
       </c>
-      <c r="AI14" s="59"/>
-      <c r="AJ14" s="59"/>
-      <c r="AK14" s="59"/>
-      <c r="AL14" s="59"/>
-      <c r="AM14" s="59"/>
-      <c r="AN14" s="59"/>
-      <c r="AO14" s="59"/>
-      <c r="AP14" s="59"/>
-      <c r="AQ14" s="59"/>
-      <c r="AR14" s="59"/>
-      <c r="AS14" s="59"/>
-      <c r="AT14" s="59"/>
-      <c r="AU14" s="59"/>
-      <c r="AV14" s="59"/>
-      <c r="AW14" s="59"/>
-      <c r="AX14" s="59"/>
-      <c r="AY14" s="59"/>
-      <c r="AZ14" s="88" t="s">
+      <c r="AI14" s="137"/>
+      <c r="AJ14" s="137"/>
+      <c r="AK14" s="137"/>
+      <c r="AL14" s="137"/>
+      <c r="AM14" s="137"/>
+      <c r="AN14" s="137"/>
+      <c r="AO14" s="137"/>
+      <c r="AP14" s="137"/>
+      <c r="AQ14" s="137"/>
+      <c r="AR14" s="137"/>
+      <c r="AS14" s="137"/>
+      <c r="AT14" s="137"/>
+      <c r="AU14" s="137"/>
+      <c r="AV14" s="137"/>
+      <c r="AW14" s="137"/>
+      <c r="AX14" s="137"/>
+      <c r="AY14" s="137"/>
+      <c r="AZ14" s="123" t="s">
         <v>41</v>
       </c>
-      <c r="BA14" s="88"/>
-      <c r="BB14" s="88"/>
-      <c r="BC14" s="88"/>
-      <c r="BD14" s="88"/>
-      <c r="BE14" s="88"/>
-      <c r="BF14" s="88"/>
-      <c r="BG14" s="88"/>
-      <c r="BH14" s="88"/>
-      <c r="BI14" s="89"/>
-      <c r="BJ14" s="90" t="s">
+      <c r="BA14" s="123"/>
+      <c r="BB14" s="123"/>
+      <c r="BC14" s="123"/>
+      <c r="BD14" s="123"/>
+      <c r="BE14" s="123"/>
+      <c r="BF14" s="123"/>
+      <c r="BG14" s="123"/>
+      <c r="BH14" s="123"/>
+      <c r="BI14" s="124"/>
+      <c r="BJ14" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="BK14" s="90"/>
-      <c r="BL14" s="90"/>
-      <c r="BM14" s="90"/>
-      <c r="BN14" s="90"/>
-      <c r="BO14" s="90"/>
-      <c r="BP14" s="90"/>
-      <c r="BQ14" s="90"/>
-      <c r="BR14" s="90"/>
-      <c r="BS14" s="90"/>
-      <c r="BT14" s="90"/>
-      <c r="BU14" s="90"/>
-      <c r="BV14" s="90"/>
-      <c r="BW14" s="90"/>
-      <c r="BX14" s="90"/>
-      <c r="BY14" s="90"/>
-      <c r="BZ14" s="90"/>
-      <c r="CA14" s="90"/>
-      <c r="CB14" s="90"/>
-      <c r="CC14" s="90"/>
-      <c r="CD14" s="90"/>
-    </row>
-    <row r="15" spans="1:82" ht="28.8" customHeight="1" thickBot="1">
-      <c r="D15" s="46" t="s">
+      <c r="BK14" s="57"/>
+      <c r="BL14" s="57"/>
+      <c r="BM14" s="57"/>
+      <c r="BN14" s="57"/>
+      <c r="BO14" s="57"/>
+      <c r="BP14" s="57"/>
+      <c r="BQ14" s="57"/>
+      <c r="BR14" s="57"/>
+      <c r="BS14" s="57"/>
+      <c r="BT14" s="57"/>
+      <c r="BU14" s="57"/>
+      <c r="BV14" s="57"/>
+      <c r="BW14" s="57"/>
+      <c r="BX14" s="57"/>
+      <c r="BY14" s="57"/>
+      <c r="BZ14" s="57"/>
+      <c r="CA14" s="57"/>
+      <c r="CB14" s="57"/>
+      <c r="CC14" s="57"/>
+      <c r="CD14" s="57"/>
+    </row>
+    <row r="15" spans="1:82" ht="28.9" customHeight="1" thickBot="1">
+      <c r="D15" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="41" t="s">
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="112" t="s">
         <v>206</v>
       </c>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="41"/>
-      <c r="AE15" s="41"/>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="41"/>
-      <c r="AH15" s="58" t="s">
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="112"/>
+      <c r="R15" s="112"/>
+      <c r="S15" s="112"/>
+      <c r="T15" s="112"/>
+      <c r="U15" s="112"/>
+      <c r="V15" s="112"/>
+      <c r="W15" s="112"/>
+      <c r="X15" s="112"/>
+      <c r="Y15" s="112"/>
+      <c r="Z15" s="112"/>
+      <c r="AA15" s="112"/>
+      <c r="AB15" s="112"/>
+      <c r="AC15" s="112"/>
+      <c r="AD15" s="112"/>
+      <c r="AE15" s="112"/>
+      <c r="AF15" s="112"/>
+      <c r="AG15" s="112"/>
+      <c r="AH15" s="136" t="s">
         <v>211</v>
       </c>
-      <c r="AI15" s="58"/>
-      <c r="AJ15" s="58"/>
-      <c r="AK15" s="58"/>
-      <c r="AL15" s="58"/>
-      <c r="AM15" s="58"/>
-      <c r="AN15" s="58"/>
-      <c r="AO15" s="58"/>
-      <c r="AP15" s="58"/>
-      <c r="AQ15" s="58"/>
-      <c r="AR15" s="58"/>
-      <c r="AS15" s="58"/>
-      <c r="AT15" s="58"/>
-      <c r="AU15" s="58"/>
-      <c r="AV15" s="58"/>
-      <c r="AW15" s="58"/>
-      <c r="AX15" s="58"/>
-      <c r="AY15" s="58"/>
-      <c r="AZ15" s="91" t="s">
+      <c r="AI15" s="136"/>
+      <c r="AJ15" s="136"/>
+      <c r="AK15" s="136"/>
+      <c r="AL15" s="136"/>
+      <c r="AM15" s="136"/>
+      <c r="AN15" s="136"/>
+      <c r="AO15" s="136"/>
+      <c r="AP15" s="136"/>
+      <c r="AQ15" s="136"/>
+      <c r="AR15" s="136"/>
+      <c r="AS15" s="136"/>
+      <c r="AT15" s="136"/>
+      <c r="AU15" s="136"/>
+      <c r="AV15" s="136"/>
+      <c r="AW15" s="136"/>
+      <c r="AX15" s="136"/>
+      <c r="AY15" s="136"/>
+      <c r="AZ15" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="BA15" s="91"/>
-      <c r="BB15" s="91"/>
-      <c r="BC15" s="91"/>
-      <c r="BD15" s="91"/>
-      <c r="BE15" s="91"/>
-      <c r="BF15" s="91"/>
-      <c r="BG15" s="91"/>
-      <c r="BH15" s="91"/>
-      <c r="BI15" s="92"/>
-      <c r="BJ15" s="93" t="s">
+      <c r="BA15" s="125"/>
+      <c r="BB15" s="125"/>
+      <c r="BC15" s="125"/>
+      <c r="BD15" s="125"/>
+      <c r="BE15" s="125"/>
+      <c r="BF15" s="125"/>
+      <c r="BG15" s="125"/>
+      <c r="BH15" s="125"/>
+      <c r="BI15" s="126"/>
+      <c r="BJ15" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="BK15" s="90"/>
-      <c r="BL15" s="90"/>
-      <c r="BM15" s="90"/>
-      <c r="BN15" s="90"/>
-      <c r="BO15" s="90"/>
-      <c r="BP15" s="90"/>
-      <c r="BQ15" s="90"/>
-      <c r="BR15" s="90"/>
-      <c r="BS15" s="90"/>
-      <c r="BT15" s="90"/>
-      <c r="BU15" s="90"/>
-      <c r="BV15" s="90"/>
-      <c r="BW15" s="90"/>
-      <c r="BX15" s="90"/>
-      <c r="BY15" s="90"/>
-      <c r="BZ15" s="90"/>
-      <c r="CA15" s="90"/>
-      <c r="CB15" s="90"/>
-      <c r="CC15" s="90"/>
-      <c r="CD15" s="90"/>
+      <c r="BK15" s="57"/>
+      <c r="BL15" s="57"/>
+      <c r="BM15" s="57"/>
+      <c r="BN15" s="57"/>
+      <c r="BO15" s="57"/>
+      <c r="BP15" s="57"/>
+      <c r="BQ15" s="57"/>
+      <c r="BR15" s="57"/>
+      <c r="BS15" s="57"/>
+      <c r="BT15" s="57"/>
+      <c r="BU15" s="57"/>
+      <c r="BV15" s="57"/>
+      <c r="BW15" s="57"/>
+      <c r="BX15" s="57"/>
+      <c r="BY15" s="57"/>
+      <c r="BZ15" s="57"/>
+      <c r="CA15" s="57"/>
+      <c r="CB15" s="57"/>
+      <c r="CC15" s="57"/>
+      <c r="CD15" s="57"/>
     </row>
     <row r="17" spans="1:70">
-      <c r="C17" s="102" t="s">
+      <c r="C17" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="104"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="69"/>
     </row>
     <row r="18" spans="1:70">
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
     </row>
     <row r="19" spans="1:70">
-      <c r="E19" s="100" t="s">
+      <c r="E19" s="65" t="s">
         <v>214</v>
       </c>
-      <c r="F19" s="101"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="95"/>
-      <c r="O19" s="95"/>
-      <c r="P19" s="95"/>
-      <c r="Q19" s="95"/>
-      <c r="R19" s="95"/>
-      <c r="S19" s="95"/>
-      <c r="T19" s="95"/>
-      <c r="U19" s="95"/>
-      <c r="V19" s="95"/>
-      <c r="W19" s="95"/>
-      <c r="X19" s="95"/>
-      <c r="Y19" s="95"/>
-      <c r="Z19" s="95"/>
-      <c r="AA19" s="96"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="61"/>
       <c r="AC19" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AE19" s="94" t="s">
+      <c r="AE19" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="AF19" s="95"/>
-      <c r="AG19" s="95"/>
-      <c r="AH19" s="95"/>
-      <c r="AI19" s="95"/>
-      <c r="AJ19" s="95"/>
-      <c r="AK19" s="95"/>
-      <c r="AL19" s="95"/>
-      <c r="AM19" s="95"/>
-      <c r="AN19" s="95"/>
-      <c r="AO19" s="95"/>
-      <c r="AP19" s="96"/>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="61"/>
     </row>
     <row r="21" spans="1:70">
-      <c r="M21" s="97" t="s">
+      <c r="M21" s="62" t="s">
         <v>218</v>
       </c>
-      <c r="N21" s="98"/>
-      <c r="O21" s="98"/>
-      <c r="P21" s="99"/>
-    </row>
-    <row r="22" spans="1:70" ht="14.4" thickBot="1"/>
-    <row r="23" spans="1:70" ht="14.4" thickBot="1">
-      <c r="E23" s="107" t="s">
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="64"/>
+    </row>
+    <row r="22" spans="1:70" ht="15" thickBot="1"/>
+    <row r="23" spans="1:70" ht="15" thickBot="1">
+      <c r="E23" s="70" t="s">
         <v>216</v>
       </c>
-      <c r="F23" s="108"/>
-      <c r="G23" s="108"/>
-      <c r="H23" s="108"/>
-      <c r="I23" s="108"/>
-      <c r="J23" s="108"/>
-      <c r="K23" s="108"/>
-      <c r="L23" s="108"/>
-      <c r="M23" s="108"/>
-      <c r="N23" s="108"/>
-      <c r="O23" s="108"/>
-      <c r="P23" s="108"/>
-      <c r="Q23" s="108"/>
-      <c r="R23" s="108"/>
-      <c r="S23" s="108"/>
-      <c r="T23" s="108"/>
-      <c r="U23" s="108"/>
-      <c r="V23" s="108"/>
-      <c r="W23" s="108"/>
-      <c r="X23" s="108"/>
-      <c r="Y23" s="108"/>
-      <c r="Z23" s="108"/>
-      <c r="AA23" s="109"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="71"/>
+      <c r="X23" s="71"/>
+      <c r="Y23" s="71"/>
+      <c r="Z23" s="71"/>
+      <c r="AA23" s="72"/>
       <c r="AC23" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="AE23" s="94" t="s">
+      <c r="AE23" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="AF23" s="95"/>
-      <c r="AG23" s="95"/>
-      <c r="AH23" s="95"/>
-      <c r="AI23" s="95"/>
-      <c r="AJ23" s="95"/>
-      <c r="AK23" s="95"/>
-      <c r="AL23" s="95"/>
-      <c r="AM23" s="95"/>
-      <c r="AN23" s="95"/>
-      <c r="AO23" s="95"/>
-      <c r="AP23" s="96"/>
-    </row>
-    <row r="24" spans="1:70" ht="14.4" thickBot="1"/>
-    <row r="25" spans="1:70" s="12" customFormat="1" ht="14.4" thickBot="1">
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="61"/>
+    </row>
+    <row r="24" spans="1:70" ht="15" thickBot="1"/>
+    <row r="25" spans="1:70" s="12" customFormat="1" ht="15.75" thickBot="1">
       <c r="A25" s="11"/>
       <c r="C25" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:70" ht="14.4" thickBot="1"/>
-    <row r="27" spans="1:70">
-      <c r="D27" s="43" t="s">
+    <row r="26" spans="1:70" ht="15" thickBot="1"/>
+    <row r="27" spans="1:70" ht="15">
+      <c r="D27" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="57" t="s">
+      <c r="E27" s="127"/>
+      <c r="F27" s="127"/>
+      <c r="G27" s="127"/>
+      <c r="H27" s="127"/>
+      <c r="I27" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="57"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="31" t="s">
+      <c r="J27" s="135"/>
+      <c r="K27" s="135"/>
+      <c r="L27" s="135"/>
+      <c r="M27" s="135"/>
+      <c r="N27" s="135"/>
+      <c r="O27" s="135"/>
+      <c r="P27" s="135"/>
+      <c r="Q27" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="R27" s="31"/>
-      <c r="S27" s="31"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="31"/>
-      <c r="Z27" s="31"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="31"/>
-      <c r="AC27" s="31"/>
-      <c r="AD27" s="31" t="s">
+      <c r="R27" s="127"/>
+      <c r="S27" s="127"/>
+      <c r="T27" s="127"/>
+      <c r="U27" s="127"/>
+      <c r="V27" s="127"/>
+      <c r="W27" s="127"/>
+      <c r="X27" s="127"/>
+      <c r="Y27" s="127"/>
+      <c r="Z27" s="127"/>
+      <c r="AA27" s="127"/>
+      <c r="AB27" s="127"/>
+      <c r="AC27" s="127"/>
+      <c r="AD27" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="AE27" s="31"/>
-      <c r="AF27" s="31"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="31"/>
-      <c r="AL27" s="31"/>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="31"/>
-      <c r="AO27" s="31"/>
-      <c r="AP27" s="31"/>
-      <c r="AQ27" s="55" t="s">
+      <c r="AE27" s="127"/>
+      <c r="AF27" s="127"/>
+      <c r="AG27" s="127"/>
+      <c r="AH27" s="127"/>
+      <c r="AI27" s="127"/>
+      <c r="AJ27" s="127"/>
+      <c r="AK27" s="127"/>
+      <c r="AL27" s="127"/>
+      <c r="AM27" s="127"/>
+      <c r="AN27" s="127"/>
+      <c r="AO27" s="127"/>
+      <c r="AP27" s="127"/>
+      <c r="AQ27" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="AR27" s="55"/>
-      <c r="AS27" s="55"/>
-      <c r="AT27" s="55"/>
-      <c r="AU27" s="55"/>
-      <c r="AV27" s="55"/>
-      <c r="AW27" s="55"/>
-      <c r="AX27" s="55"/>
-      <c r="AY27" s="55"/>
-      <c r="AZ27" s="55"/>
-      <c r="BA27" s="55"/>
-      <c r="BB27" s="56"/>
+      <c r="AR27" s="121"/>
+      <c r="AS27" s="121"/>
+      <c r="AT27" s="121"/>
+      <c r="AU27" s="121"/>
+      <c r="AV27" s="121"/>
+      <c r="AW27" s="121"/>
+      <c r="AX27" s="121"/>
+      <c r="AY27" s="121"/>
+      <c r="AZ27" s="121"/>
+      <c r="BA27" s="121"/>
+      <c r="BB27" s="122"/>
     </row>
     <row r="28" spans="1:70">
-      <c r="D28" s="37" t="s">
+      <c r="D28" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="33" t="s">
+      <c r="E28" s="128"/>
+      <c r="F28" s="128"/>
+      <c r="G28" s="128"/>
+      <c r="H28" s="128"/>
+      <c r="I28" s="130" t="s">
         <v>29</v>
       </c>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="38" t="s">
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
+      <c r="L28" s="130"/>
+      <c r="M28" s="130"/>
+      <c r="N28" s="130"/>
+      <c r="O28" s="130"/>
+      <c r="P28" s="130"/>
+      <c r="Q28" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="38"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="38"/>
-      <c r="X28" s="38"/>
-      <c r="Y28" s="38"/>
-      <c r="Z28" s="38"/>
-      <c r="AA28" s="38"/>
-      <c r="AB28" s="38"/>
-      <c r="AC28" s="38"/>
-      <c r="AD28" s="33" t="s">
+      <c r="R28" s="128"/>
+      <c r="S28" s="128"/>
+      <c r="T28" s="128"/>
+      <c r="U28" s="128"/>
+      <c r="V28" s="128"/>
+      <c r="W28" s="128"/>
+      <c r="X28" s="128"/>
+      <c r="Y28" s="128"/>
+      <c r="Z28" s="128"/>
+      <c r="AA28" s="128"/>
+      <c r="AB28" s="128"/>
+      <c r="AC28" s="128"/>
+      <c r="AD28" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="AE28" s="33"/>
-      <c r="AF28" s="33"/>
-      <c r="AG28" s="33"/>
-      <c r="AH28" s="33"/>
-      <c r="AI28" s="33"/>
-      <c r="AJ28" s="33"/>
-      <c r="AK28" s="33"/>
-      <c r="AL28" s="33"/>
-      <c r="AM28" s="33"/>
-      <c r="AN28" s="33"/>
-      <c r="AO28" s="33"/>
-      <c r="AP28" s="33"/>
-      <c r="AQ28" s="50" t="s">
+      <c r="AE28" s="130"/>
+      <c r="AF28" s="130"/>
+      <c r="AG28" s="130"/>
+      <c r="AH28" s="130"/>
+      <c r="AI28" s="130"/>
+      <c r="AJ28" s="130"/>
+      <c r="AK28" s="130"/>
+      <c r="AL28" s="130"/>
+      <c r="AM28" s="130"/>
+      <c r="AN28" s="130"/>
+      <c r="AO28" s="130"/>
+      <c r="AP28" s="130"/>
+      <c r="AQ28" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="AR28" s="50"/>
-      <c r="AS28" s="50"/>
-      <c r="AT28" s="50"/>
-      <c r="AU28" s="50"/>
-      <c r="AV28" s="50"/>
-      <c r="AW28" s="50"/>
-      <c r="AX28" s="50"/>
-      <c r="AY28" s="50"/>
-      <c r="AZ28" s="50"/>
-      <c r="BA28" s="50"/>
-      <c r="BB28" s="51"/>
+      <c r="AR28" s="116"/>
+      <c r="AS28" s="116"/>
+      <c r="AT28" s="116"/>
+      <c r="AU28" s="116"/>
+      <c r="AV28" s="116"/>
+      <c r="AW28" s="116"/>
+      <c r="AX28" s="116"/>
+      <c r="AY28" s="116"/>
+      <c r="AZ28" s="116"/>
+      <c r="BA28" s="116"/>
+      <c r="BB28" s="117"/>
       <c r="BC28" s="13" t="s">
         <v>48</v>
       </c>
@@ -5022,67 +5019,67 @@
       <c r="BR28" s="13"/>
     </row>
     <row r="29" spans="1:70">
-      <c r="D29" s="37" t="s">
+      <c r="D29" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="33" t="s">
+      <c r="E29" s="128"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="38" t="s">
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="130"/>
+      <c r="M29" s="130"/>
+      <c r="N29" s="130"/>
+      <c r="O29" s="130"/>
+      <c r="P29" s="130"/>
+      <c r="Q29" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="38"/>
-      <c r="V29" s="38"/>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="38"/>
-      <c r="AA29" s="38"/>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="38"/>
-      <c r="AD29" s="33" t="s">
+      <c r="R29" s="128"/>
+      <c r="S29" s="128"/>
+      <c r="T29" s="128"/>
+      <c r="U29" s="128"/>
+      <c r="V29" s="128"/>
+      <c r="W29" s="128"/>
+      <c r="X29" s="128"/>
+      <c r="Y29" s="128"/>
+      <c r="Z29" s="128"/>
+      <c r="AA29" s="128"/>
+      <c r="AB29" s="128"/>
+      <c r="AC29" s="128"/>
+      <c r="AD29" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="AE29" s="33"/>
-      <c r="AF29" s="33"/>
-      <c r="AG29" s="33"/>
-      <c r="AH29" s="33"/>
-      <c r="AI29" s="33"/>
-      <c r="AJ29" s="33"/>
-      <c r="AK29" s="33"/>
-      <c r="AL29" s="33"/>
-      <c r="AM29" s="33"/>
-      <c r="AN29" s="33"/>
-      <c r="AO29" s="33"/>
-      <c r="AP29" s="33"/>
-      <c r="AQ29" s="50" t="s">
+      <c r="AE29" s="130"/>
+      <c r="AF29" s="130"/>
+      <c r="AG29" s="130"/>
+      <c r="AH29" s="130"/>
+      <c r="AI29" s="130"/>
+      <c r="AJ29" s="130"/>
+      <c r="AK29" s="130"/>
+      <c r="AL29" s="130"/>
+      <c r="AM29" s="130"/>
+      <c r="AN29" s="130"/>
+      <c r="AO29" s="130"/>
+      <c r="AP29" s="130"/>
+      <c r="AQ29" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="AR29" s="50"/>
-      <c r="AS29" s="50"/>
-      <c r="AT29" s="50"/>
-      <c r="AU29" s="50"/>
-      <c r="AV29" s="50"/>
-      <c r="AW29" s="50"/>
-      <c r="AX29" s="50"/>
-      <c r="AY29" s="50"/>
-      <c r="AZ29" s="50"/>
-      <c r="BA29" s="50"/>
-      <c r="BB29" s="51"/>
+      <c r="AR29" s="116"/>
+      <c r="AS29" s="116"/>
+      <c r="AT29" s="116"/>
+      <c r="AU29" s="116"/>
+      <c r="AV29" s="116"/>
+      <c r="AW29" s="116"/>
+      <c r="AX29" s="116"/>
+      <c r="AY29" s="116"/>
+      <c r="AZ29" s="116"/>
+      <c r="BA29" s="116"/>
+      <c r="BB29" s="117"/>
       <c r="BC29" s="13" t="s">
         <v>49</v>
       </c>
@@ -5102,68 +5099,68 @@
       <c r="BQ29" s="13"/>
       <c r="BR29" s="13"/>
     </row>
-    <row r="30" spans="1:70" ht="14.4" thickBot="1">
-      <c r="D30" s="35" t="s">
+    <row r="30" spans="1:70" ht="15" thickBot="1">
+      <c r="D30" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36" t="s">
+      <c r="E30" s="129"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="129"/>
+      <c r="H30" s="129"/>
+      <c r="I30" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="36" t="s">
+      <c r="J30" s="129"/>
+      <c r="K30" s="129"/>
+      <c r="L30" s="129"/>
+      <c r="M30" s="129"/>
+      <c r="N30" s="129"/>
+      <c r="O30" s="129"/>
+      <c r="P30" s="129"/>
+      <c r="Q30" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="R30" s="36"/>
-      <c r="S30" s="36"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="36"/>
-      <c r="Y30" s="36"/>
-      <c r="Z30" s="36"/>
-      <c r="AA30" s="36"/>
-      <c r="AB30" s="36"/>
-      <c r="AC30" s="36"/>
-      <c r="AD30" s="29" t="s">
+      <c r="R30" s="129"/>
+      <c r="S30" s="129"/>
+      <c r="T30" s="129"/>
+      <c r="U30" s="129"/>
+      <c r="V30" s="129"/>
+      <c r="W30" s="129"/>
+      <c r="X30" s="129"/>
+      <c r="Y30" s="129"/>
+      <c r="Z30" s="129"/>
+      <c r="AA30" s="129"/>
+      <c r="AB30" s="129"/>
+      <c r="AC30" s="129"/>
+      <c r="AD30" s="131" t="s">
         <v>39</v>
       </c>
-      <c r="AE30" s="29"/>
-      <c r="AF30" s="29"/>
-      <c r="AG30" s="29"/>
-      <c r="AH30" s="29"/>
-      <c r="AI30" s="29"/>
-      <c r="AJ30" s="29"/>
-      <c r="AK30" s="29"/>
-      <c r="AL30" s="29"/>
-      <c r="AM30" s="29"/>
-      <c r="AN30" s="29"/>
-      <c r="AO30" s="29"/>
-      <c r="AP30" s="29"/>
-      <c r="AQ30" s="52" t="s">
+      <c r="AE30" s="131"/>
+      <c r="AF30" s="131"/>
+      <c r="AG30" s="131"/>
+      <c r="AH30" s="131"/>
+      <c r="AI30" s="131"/>
+      <c r="AJ30" s="131"/>
+      <c r="AK30" s="131"/>
+      <c r="AL30" s="131"/>
+      <c r="AM30" s="131"/>
+      <c r="AN30" s="131"/>
+      <c r="AO30" s="131"/>
+      <c r="AP30" s="131"/>
+      <c r="AQ30" s="118" t="s">
         <v>45</v>
       </c>
-      <c r="AR30" s="52"/>
-      <c r="AS30" s="52"/>
-      <c r="AT30" s="52"/>
-      <c r="AU30" s="52"/>
-      <c r="AV30" s="52"/>
-      <c r="AW30" s="52"/>
-      <c r="AX30" s="52"/>
-      <c r="AY30" s="52"/>
-      <c r="AZ30" s="52"/>
-      <c r="BA30" s="52"/>
-      <c r="BB30" s="53"/>
+      <c r="AR30" s="118"/>
+      <c r="AS30" s="118"/>
+      <c r="AT30" s="118"/>
+      <c r="AU30" s="118"/>
+      <c r="AV30" s="118"/>
+      <c r="AW30" s="118"/>
+      <c r="AX30" s="118"/>
+      <c r="AY30" s="118"/>
+      <c r="AZ30" s="118"/>
+      <c r="BA30" s="118"/>
+      <c r="BB30" s="119"/>
       <c r="BC30" s="13" t="s">
         <v>50</v>
       </c>
@@ -5183,815 +5180,815 @@
       <c r="BQ30" s="13"/>
       <c r="BR30" s="13"/>
     </row>
-    <row r="31" spans="1:70" ht="14.4" thickBot="1"/>
-    <row r="32" spans="1:70" s="16" customFormat="1" ht="14.4" thickBot="1">
+    <row r="31" spans="1:70" ht="15" thickBot="1"/>
+    <row r="32" spans="1:70" s="16" customFormat="1" ht="15.75" thickBot="1">
       <c r="A32" s="15"/>
       <c r="C32" s="17" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:68" ht="14.4" thickBot="1"/>
-    <row r="34" spans="1:68">
-      <c r="E34" s="54" t="s">
+    <row r="33" spans="1:68" ht="15" thickBot="1"/>
+    <row r="34" spans="1:68" ht="15">
+      <c r="E34" s="120" t="s">
         <v>52</v>
       </c>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="44" t="s">
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108"/>
+      <c r="O34" s="108"/>
+      <c r="P34" s="108"/>
+      <c r="Q34" s="108"/>
+      <c r="R34" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="S34" s="44"/>
-      <c r="T34" s="44"/>
-      <c r="U34" s="44"/>
-      <c r="V34" s="44"/>
-      <c r="W34" s="44"/>
-      <c r="X34" s="44"/>
-      <c r="Y34" s="44"/>
-      <c r="Z34" s="44"/>
-      <c r="AA34" s="44"/>
-      <c r="AB34" s="44"/>
-      <c r="AC34" s="44"/>
-      <c r="AD34" s="44"/>
-      <c r="AE34" s="44"/>
-      <c r="AF34" s="44"/>
-      <c r="AG34" s="44"/>
-      <c r="AH34" s="44"/>
-      <c r="AI34" s="44"/>
-      <c r="AJ34" s="44"/>
-      <c r="AK34" s="44"/>
-      <c r="AL34" s="44"/>
-      <c r="AM34" s="44"/>
-      <c r="AN34" s="44"/>
-      <c r="AO34" s="44"/>
-      <c r="AP34" s="44" t="s">
+      <c r="S34" s="108"/>
+      <c r="T34" s="108"/>
+      <c r="U34" s="108"/>
+      <c r="V34" s="108"/>
+      <c r="W34" s="108"/>
+      <c r="X34" s="108"/>
+      <c r="Y34" s="108"/>
+      <c r="Z34" s="108"/>
+      <c r="AA34" s="108"/>
+      <c r="AB34" s="108"/>
+      <c r="AC34" s="108"/>
+      <c r="AD34" s="108"/>
+      <c r="AE34" s="108"/>
+      <c r="AF34" s="108"/>
+      <c r="AG34" s="108"/>
+      <c r="AH34" s="108"/>
+      <c r="AI34" s="108"/>
+      <c r="AJ34" s="108"/>
+      <c r="AK34" s="108"/>
+      <c r="AL34" s="108"/>
+      <c r="AM34" s="108"/>
+      <c r="AN34" s="108"/>
+      <c r="AO34" s="108"/>
+      <c r="AP34" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="AQ34" s="44"/>
-      <c r="AR34" s="44"/>
-      <c r="AS34" s="44"/>
-      <c r="AT34" s="44"/>
-      <c r="AU34" s="44"/>
-      <c r="AV34" s="44"/>
-      <c r="AW34" s="44"/>
-      <c r="AX34" s="44"/>
-      <c r="AY34" s="44"/>
-      <c r="AZ34" s="44"/>
-      <c r="BA34" s="44"/>
-      <c r="BB34" s="44"/>
-      <c r="BC34" s="44"/>
-      <c r="BD34" s="44"/>
-      <c r="BE34" s="44"/>
-      <c r="BF34" s="44"/>
-      <c r="BG34" s="44"/>
-      <c r="BH34" s="44"/>
-      <c r="BI34" s="44"/>
-      <c r="BJ34" s="44"/>
-      <c r="BK34" s="44"/>
-      <c r="BL34" s="44"/>
-      <c r="BM34" s="44"/>
-      <c r="BN34" s="44"/>
-      <c r="BO34" s="44"/>
-      <c r="BP34" s="45"/>
-    </row>
-    <row r="35" spans="1:68">
-      <c r="E35" s="48" t="s">
+      <c r="AQ34" s="108"/>
+      <c r="AR34" s="108"/>
+      <c r="AS34" s="108"/>
+      <c r="AT34" s="108"/>
+      <c r="AU34" s="108"/>
+      <c r="AV34" s="108"/>
+      <c r="AW34" s="108"/>
+      <c r="AX34" s="108"/>
+      <c r="AY34" s="108"/>
+      <c r="AZ34" s="108"/>
+      <c r="BA34" s="108"/>
+      <c r="BB34" s="108"/>
+      <c r="BC34" s="108"/>
+      <c r="BD34" s="108"/>
+      <c r="BE34" s="108"/>
+      <c r="BF34" s="108"/>
+      <c r="BG34" s="108"/>
+      <c r="BH34" s="108"/>
+      <c r="BI34" s="108"/>
+      <c r="BJ34" s="108"/>
+      <c r="BK34" s="108"/>
+      <c r="BL34" s="108"/>
+      <c r="BM34" s="108"/>
+      <c r="BN34" s="108"/>
+      <c r="BO34" s="108"/>
+      <c r="BP34" s="113"/>
+    </row>
+    <row r="35" spans="1:68" ht="15">
+      <c r="E35" s="110" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="49"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="39" t="s">
+      <c r="F35" s="111"/>
+      <c r="G35" s="111"/>
+      <c r="H35" s="111"/>
+      <c r="I35" s="111"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="111"/>
+      <c r="M35" s="111"/>
+      <c r="N35" s="111"/>
+      <c r="O35" s="111"/>
+      <c r="P35" s="111"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="109" t="s">
         <v>56</v>
       </c>
-      <c r="S35" s="39"/>
-      <c r="T35" s="39"/>
-      <c r="U35" s="39"/>
-      <c r="V35" s="39"/>
-      <c r="W35" s="39"/>
-      <c r="X35" s="39"/>
-      <c r="Y35" s="39"/>
-      <c r="Z35" s="39"/>
-      <c r="AA35" s="39"/>
-      <c r="AB35" s="39"/>
-      <c r="AC35" s="39"/>
-      <c r="AD35" s="39"/>
-      <c r="AE35" s="39"/>
-      <c r="AF35" s="39"/>
-      <c r="AG35" s="39"/>
-      <c r="AH35" s="39"/>
-      <c r="AI35" s="39"/>
-      <c r="AJ35" s="39"/>
-      <c r="AK35" s="39"/>
-      <c r="AL35" s="39"/>
-      <c r="AM35" s="39"/>
-      <c r="AN35" s="39"/>
-      <c r="AO35" s="39"/>
-      <c r="AP35" s="39" t="s">
+      <c r="S35" s="109"/>
+      <c r="T35" s="109"/>
+      <c r="U35" s="109"/>
+      <c r="V35" s="109"/>
+      <c r="W35" s="109"/>
+      <c r="X35" s="109"/>
+      <c r="Y35" s="109"/>
+      <c r="Z35" s="109"/>
+      <c r="AA35" s="109"/>
+      <c r="AB35" s="109"/>
+      <c r="AC35" s="109"/>
+      <c r="AD35" s="109"/>
+      <c r="AE35" s="109"/>
+      <c r="AF35" s="109"/>
+      <c r="AG35" s="109"/>
+      <c r="AH35" s="109"/>
+      <c r="AI35" s="109"/>
+      <c r="AJ35" s="109"/>
+      <c r="AK35" s="109"/>
+      <c r="AL35" s="109"/>
+      <c r="AM35" s="109"/>
+      <c r="AN35" s="109"/>
+      <c r="AO35" s="109"/>
+      <c r="AP35" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="AQ35" s="39"/>
-      <c r="AR35" s="39"/>
-      <c r="AS35" s="39"/>
-      <c r="AT35" s="39"/>
-      <c r="AU35" s="39"/>
-      <c r="AV35" s="39"/>
-      <c r="AW35" s="39"/>
-      <c r="AX35" s="39"/>
-      <c r="AY35" s="39"/>
-      <c r="AZ35" s="39"/>
-      <c r="BA35" s="39"/>
-      <c r="BB35" s="39"/>
-      <c r="BC35" s="39"/>
-      <c r="BD35" s="39"/>
-      <c r="BE35" s="39"/>
-      <c r="BF35" s="39"/>
-      <c r="BG35" s="39"/>
-      <c r="BH35" s="39"/>
-      <c r="BI35" s="39"/>
-      <c r="BJ35" s="39"/>
-      <c r="BK35" s="39"/>
-      <c r="BL35" s="39"/>
-      <c r="BM35" s="39"/>
-      <c r="BN35" s="39"/>
-      <c r="BO35" s="39"/>
-      <c r="BP35" s="40"/>
-    </row>
-    <row r="36" spans="1:68">
-      <c r="E36" s="48" t="s">
+      <c r="AQ35" s="109"/>
+      <c r="AR35" s="109"/>
+      <c r="AS35" s="109"/>
+      <c r="AT35" s="109"/>
+      <c r="AU35" s="109"/>
+      <c r="AV35" s="109"/>
+      <c r="AW35" s="109"/>
+      <c r="AX35" s="109"/>
+      <c r="AY35" s="109"/>
+      <c r="AZ35" s="109"/>
+      <c r="BA35" s="109"/>
+      <c r="BB35" s="109"/>
+      <c r="BC35" s="109"/>
+      <c r="BD35" s="109"/>
+      <c r="BE35" s="109"/>
+      <c r="BF35" s="109"/>
+      <c r="BG35" s="109"/>
+      <c r="BH35" s="109"/>
+      <c r="BI35" s="109"/>
+      <c r="BJ35" s="109"/>
+      <c r="BK35" s="109"/>
+      <c r="BL35" s="109"/>
+      <c r="BM35" s="109"/>
+      <c r="BN35" s="109"/>
+      <c r="BO35" s="109"/>
+      <c r="BP35" s="114"/>
+    </row>
+    <row r="36" spans="1:68" ht="15">
+      <c r="E36" s="110" t="s">
         <v>58</v>
       </c>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="49"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="39" t="s">
+      <c r="F36" s="111"/>
+      <c r="G36" s="111"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+      <c r="M36" s="111"/>
+      <c r="N36" s="111"/>
+      <c r="O36" s="111"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="109" t="s">
         <v>59</v>
       </c>
-      <c r="S36" s="39"/>
-      <c r="T36" s="39"/>
-      <c r="U36" s="39"/>
-      <c r="V36" s="39"/>
-      <c r="W36" s="39"/>
-      <c r="X36" s="39"/>
-      <c r="Y36" s="39"/>
-      <c r="Z36" s="39"/>
-      <c r="AA36" s="39"/>
-      <c r="AB36" s="39"/>
-      <c r="AC36" s="39"/>
-      <c r="AD36" s="39"/>
-      <c r="AE36" s="39"/>
-      <c r="AF36" s="39"/>
-      <c r="AG36" s="39"/>
-      <c r="AH36" s="39"/>
-      <c r="AI36" s="39"/>
-      <c r="AJ36" s="39"/>
-      <c r="AK36" s="39"/>
-      <c r="AL36" s="39"/>
-      <c r="AM36" s="39"/>
-      <c r="AN36" s="39"/>
-      <c r="AO36" s="39"/>
-      <c r="AP36" s="39" t="s">
+      <c r="S36" s="109"/>
+      <c r="T36" s="109"/>
+      <c r="U36" s="109"/>
+      <c r="V36" s="109"/>
+      <c r="W36" s="109"/>
+      <c r="X36" s="109"/>
+      <c r="Y36" s="109"/>
+      <c r="Z36" s="109"/>
+      <c r="AA36" s="109"/>
+      <c r="AB36" s="109"/>
+      <c r="AC36" s="109"/>
+      <c r="AD36" s="109"/>
+      <c r="AE36" s="109"/>
+      <c r="AF36" s="109"/>
+      <c r="AG36" s="109"/>
+      <c r="AH36" s="109"/>
+      <c r="AI36" s="109"/>
+      <c r="AJ36" s="109"/>
+      <c r="AK36" s="109"/>
+      <c r="AL36" s="109"/>
+      <c r="AM36" s="109"/>
+      <c r="AN36" s="109"/>
+      <c r="AO36" s="109"/>
+      <c r="AP36" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="AQ36" s="39"/>
-      <c r="AR36" s="39"/>
-      <c r="AS36" s="39"/>
-      <c r="AT36" s="39"/>
-      <c r="AU36" s="39"/>
-      <c r="AV36" s="39"/>
-      <c r="AW36" s="39"/>
-      <c r="AX36" s="39"/>
-      <c r="AY36" s="39"/>
-      <c r="AZ36" s="39"/>
-      <c r="BA36" s="39"/>
-      <c r="BB36" s="39"/>
-      <c r="BC36" s="39"/>
-      <c r="BD36" s="39"/>
-      <c r="BE36" s="39"/>
-      <c r="BF36" s="39"/>
-      <c r="BG36" s="39"/>
-      <c r="BH36" s="39"/>
-      <c r="BI36" s="39"/>
-      <c r="BJ36" s="39"/>
-      <c r="BK36" s="39"/>
-      <c r="BL36" s="39"/>
-      <c r="BM36" s="39"/>
-      <c r="BN36" s="39"/>
-      <c r="BO36" s="39"/>
-      <c r="BP36" s="40"/>
-    </row>
-    <row r="37" spans="1:68">
-      <c r="E37" s="48" t="s">
+      <c r="AQ36" s="109"/>
+      <c r="AR36" s="109"/>
+      <c r="AS36" s="109"/>
+      <c r="AT36" s="109"/>
+      <c r="AU36" s="109"/>
+      <c r="AV36" s="109"/>
+      <c r="AW36" s="109"/>
+      <c r="AX36" s="109"/>
+      <c r="AY36" s="109"/>
+      <c r="AZ36" s="109"/>
+      <c r="BA36" s="109"/>
+      <c r="BB36" s="109"/>
+      <c r="BC36" s="109"/>
+      <c r="BD36" s="109"/>
+      <c r="BE36" s="109"/>
+      <c r="BF36" s="109"/>
+      <c r="BG36" s="109"/>
+      <c r="BH36" s="109"/>
+      <c r="BI36" s="109"/>
+      <c r="BJ36" s="109"/>
+      <c r="BK36" s="109"/>
+      <c r="BL36" s="109"/>
+      <c r="BM36" s="109"/>
+      <c r="BN36" s="109"/>
+      <c r="BO36" s="109"/>
+      <c r="BP36" s="114"/>
+    </row>
+    <row r="37" spans="1:68" ht="15">
+      <c r="E37" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="49"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="39" t="s">
+      <c r="F37" s="111"/>
+      <c r="G37" s="111"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="111"/>
+      <c r="J37" s="111"/>
+      <c r="K37" s="111"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="111"/>
+      <c r="N37" s="111"/>
+      <c r="O37" s="111"/>
+      <c r="P37" s="111"/>
+      <c r="Q37" s="111"/>
+      <c r="R37" s="109" t="s">
         <v>62</v>
       </c>
-      <c r="S37" s="39"/>
-      <c r="T37" s="39"/>
-      <c r="U37" s="39"/>
-      <c r="V37" s="39"/>
-      <c r="W37" s="39"/>
-      <c r="X37" s="39"/>
-      <c r="Y37" s="39"/>
-      <c r="Z37" s="39"/>
-      <c r="AA37" s="39"/>
-      <c r="AB37" s="39"/>
-      <c r="AC37" s="39"/>
-      <c r="AD37" s="39"/>
-      <c r="AE37" s="39"/>
-      <c r="AF37" s="39"/>
-      <c r="AG37" s="39"/>
-      <c r="AH37" s="39"/>
-      <c r="AI37" s="39"/>
-      <c r="AJ37" s="39"/>
-      <c r="AK37" s="39"/>
-      <c r="AL37" s="39"/>
-      <c r="AM37" s="39"/>
-      <c r="AN37" s="39"/>
-      <c r="AO37" s="39"/>
-      <c r="AP37" s="39" t="s">
+      <c r="S37" s="109"/>
+      <c r="T37" s="109"/>
+      <c r="U37" s="109"/>
+      <c r="V37" s="109"/>
+      <c r="W37" s="109"/>
+      <c r="X37" s="109"/>
+      <c r="Y37" s="109"/>
+      <c r="Z37" s="109"/>
+      <c r="AA37" s="109"/>
+      <c r="AB37" s="109"/>
+      <c r="AC37" s="109"/>
+      <c r="AD37" s="109"/>
+      <c r="AE37" s="109"/>
+      <c r="AF37" s="109"/>
+      <c r="AG37" s="109"/>
+      <c r="AH37" s="109"/>
+      <c r="AI37" s="109"/>
+      <c r="AJ37" s="109"/>
+      <c r="AK37" s="109"/>
+      <c r="AL37" s="109"/>
+      <c r="AM37" s="109"/>
+      <c r="AN37" s="109"/>
+      <c r="AO37" s="109"/>
+      <c r="AP37" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="AQ37" s="39"/>
-      <c r="AR37" s="39"/>
-      <c r="AS37" s="39"/>
-      <c r="AT37" s="39"/>
-      <c r="AU37" s="39"/>
-      <c r="AV37" s="39"/>
-      <c r="AW37" s="39"/>
-      <c r="AX37" s="39"/>
-      <c r="AY37" s="39"/>
-      <c r="AZ37" s="39"/>
-      <c r="BA37" s="39"/>
-      <c r="BB37" s="39"/>
-      <c r="BC37" s="39"/>
-      <c r="BD37" s="39"/>
-      <c r="BE37" s="39"/>
-      <c r="BF37" s="39"/>
-      <c r="BG37" s="39"/>
-      <c r="BH37" s="39"/>
-      <c r="BI37" s="39"/>
-      <c r="BJ37" s="39"/>
-      <c r="BK37" s="39"/>
-      <c r="BL37" s="39"/>
-      <c r="BM37" s="39"/>
-      <c r="BN37" s="39"/>
-      <c r="BO37" s="39"/>
-      <c r="BP37" s="40"/>
-    </row>
-    <row r="38" spans="1:68">
-      <c r="E38" s="48" t="s">
+      <c r="AQ37" s="109"/>
+      <c r="AR37" s="109"/>
+      <c r="AS37" s="109"/>
+      <c r="AT37" s="109"/>
+      <c r="AU37" s="109"/>
+      <c r="AV37" s="109"/>
+      <c r="AW37" s="109"/>
+      <c r="AX37" s="109"/>
+      <c r="AY37" s="109"/>
+      <c r="AZ37" s="109"/>
+      <c r="BA37" s="109"/>
+      <c r="BB37" s="109"/>
+      <c r="BC37" s="109"/>
+      <c r="BD37" s="109"/>
+      <c r="BE37" s="109"/>
+      <c r="BF37" s="109"/>
+      <c r="BG37" s="109"/>
+      <c r="BH37" s="109"/>
+      <c r="BI37" s="109"/>
+      <c r="BJ37" s="109"/>
+      <c r="BK37" s="109"/>
+      <c r="BL37" s="109"/>
+      <c r="BM37" s="109"/>
+      <c r="BN37" s="109"/>
+      <c r="BO37" s="109"/>
+      <c r="BP37" s="114"/>
+    </row>
+    <row r="38" spans="1:68" ht="15">
+      <c r="E38" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="49"/>
-      <c r="P38" s="49"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="39" t="s">
+      <c r="F38" s="111"/>
+      <c r="G38" s="111"/>
+      <c r="H38" s="111"/>
+      <c r="I38" s="111"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="111"/>
+      <c r="L38" s="111"/>
+      <c r="M38" s="111"/>
+      <c r="N38" s="111"/>
+      <c r="O38" s="111"/>
+      <c r="P38" s="111"/>
+      <c r="Q38" s="111"/>
+      <c r="R38" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="S38" s="39"/>
-      <c r="T38" s="39"/>
-      <c r="U38" s="39"/>
-      <c r="V38" s="39"/>
-      <c r="W38" s="39"/>
-      <c r="X38" s="39"/>
-      <c r="Y38" s="39"/>
-      <c r="Z38" s="39"/>
-      <c r="AA38" s="39"/>
-      <c r="AB38" s="39"/>
-      <c r="AC38" s="39"/>
-      <c r="AD38" s="39"/>
-      <c r="AE38" s="39"/>
-      <c r="AF38" s="39"/>
-      <c r="AG38" s="39"/>
-      <c r="AH38" s="39"/>
-      <c r="AI38" s="39"/>
-      <c r="AJ38" s="39"/>
-      <c r="AK38" s="39"/>
-      <c r="AL38" s="39"/>
-      <c r="AM38" s="39"/>
-      <c r="AN38" s="39"/>
-      <c r="AO38" s="39"/>
-      <c r="AP38" s="39" t="s">
+      <c r="S38" s="109"/>
+      <c r="T38" s="109"/>
+      <c r="U38" s="109"/>
+      <c r="V38" s="109"/>
+      <c r="W38" s="109"/>
+      <c r="X38" s="109"/>
+      <c r="Y38" s="109"/>
+      <c r="Z38" s="109"/>
+      <c r="AA38" s="109"/>
+      <c r="AB38" s="109"/>
+      <c r="AC38" s="109"/>
+      <c r="AD38" s="109"/>
+      <c r="AE38" s="109"/>
+      <c r="AF38" s="109"/>
+      <c r="AG38" s="109"/>
+      <c r="AH38" s="109"/>
+      <c r="AI38" s="109"/>
+      <c r="AJ38" s="109"/>
+      <c r="AK38" s="109"/>
+      <c r="AL38" s="109"/>
+      <c r="AM38" s="109"/>
+      <c r="AN38" s="109"/>
+      <c r="AO38" s="109"/>
+      <c r="AP38" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="AQ38" s="39"/>
-      <c r="AR38" s="39"/>
-      <c r="AS38" s="39"/>
-      <c r="AT38" s="39"/>
-      <c r="AU38" s="39"/>
-      <c r="AV38" s="39"/>
-      <c r="AW38" s="39"/>
-      <c r="AX38" s="39"/>
-      <c r="AY38" s="39"/>
-      <c r="AZ38" s="39"/>
-      <c r="BA38" s="39"/>
-      <c r="BB38" s="39"/>
-      <c r="BC38" s="39"/>
-      <c r="BD38" s="39"/>
-      <c r="BE38" s="39"/>
-      <c r="BF38" s="39"/>
-      <c r="BG38" s="39"/>
-      <c r="BH38" s="39"/>
-      <c r="BI38" s="39"/>
-      <c r="BJ38" s="39"/>
-      <c r="BK38" s="39"/>
-      <c r="BL38" s="39"/>
-      <c r="BM38" s="39"/>
-      <c r="BN38" s="39"/>
-      <c r="BO38" s="39"/>
-      <c r="BP38" s="40"/>
-    </row>
-    <row r="39" spans="1:68">
-      <c r="E39" s="48" t="s">
+      <c r="AQ38" s="109"/>
+      <c r="AR38" s="109"/>
+      <c r="AS38" s="109"/>
+      <c r="AT38" s="109"/>
+      <c r="AU38" s="109"/>
+      <c r="AV38" s="109"/>
+      <c r="AW38" s="109"/>
+      <c r="AX38" s="109"/>
+      <c r="AY38" s="109"/>
+      <c r="AZ38" s="109"/>
+      <c r="BA38" s="109"/>
+      <c r="BB38" s="109"/>
+      <c r="BC38" s="109"/>
+      <c r="BD38" s="109"/>
+      <c r="BE38" s="109"/>
+      <c r="BF38" s="109"/>
+      <c r="BG38" s="109"/>
+      <c r="BH38" s="109"/>
+      <c r="BI38" s="109"/>
+      <c r="BJ38" s="109"/>
+      <c r="BK38" s="109"/>
+      <c r="BL38" s="109"/>
+      <c r="BM38" s="109"/>
+      <c r="BN38" s="109"/>
+      <c r="BO38" s="109"/>
+      <c r="BP38" s="114"/>
+    </row>
+    <row r="39" spans="1:68" ht="15">
+      <c r="E39" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="49"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="39" t="s">
+      <c r="F39" s="111"/>
+      <c r="G39" s="111"/>
+      <c r="H39" s="111"/>
+      <c r="I39" s="111"/>
+      <c r="J39" s="111"/>
+      <c r="K39" s="111"/>
+      <c r="L39" s="111"/>
+      <c r="M39" s="111"/>
+      <c r="N39" s="111"/>
+      <c r="O39" s="111"/>
+      <c r="P39" s="111"/>
+      <c r="Q39" s="111"/>
+      <c r="R39" s="109" t="s">
         <v>68</v>
       </c>
-      <c r="S39" s="39"/>
-      <c r="T39" s="39"/>
-      <c r="U39" s="39"/>
-      <c r="V39" s="39"/>
-      <c r="W39" s="39"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="39"/>
-      <c r="Z39" s="39"/>
-      <c r="AA39" s="39"/>
-      <c r="AB39" s="39"/>
-      <c r="AC39" s="39"/>
-      <c r="AD39" s="39"/>
-      <c r="AE39" s="39"/>
-      <c r="AF39" s="39"/>
-      <c r="AG39" s="39"/>
-      <c r="AH39" s="39"/>
-      <c r="AI39" s="39"/>
-      <c r="AJ39" s="39"/>
-      <c r="AK39" s="39"/>
-      <c r="AL39" s="39"/>
-      <c r="AM39" s="39"/>
-      <c r="AN39" s="39"/>
-      <c r="AO39" s="39"/>
-      <c r="AP39" s="39" t="s">
+      <c r="S39" s="109"/>
+      <c r="T39" s="109"/>
+      <c r="U39" s="109"/>
+      <c r="V39" s="109"/>
+      <c r="W39" s="109"/>
+      <c r="X39" s="109"/>
+      <c r="Y39" s="109"/>
+      <c r="Z39" s="109"/>
+      <c r="AA39" s="109"/>
+      <c r="AB39" s="109"/>
+      <c r="AC39" s="109"/>
+      <c r="AD39" s="109"/>
+      <c r="AE39" s="109"/>
+      <c r="AF39" s="109"/>
+      <c r="AG39" s="109"/>
+      <c r="AH39" s="109"/>
+      <c r="AI39" s="109"/>
+      <c r="AJ39" s="109"/>
+      <c r="AK39" s="109"/>
+      <c r="AL39" s="109"/>
+      <c r="AM39" s="109"/>
+      <c r="AN39" s="109"/>
+      <c r="AO39" s="109"/>
+      <c r="AP39" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="AQ39" s="39"/>
-      <c r="AR39" s="39"/>
-      <c r="AS39" s="39"/>
-      <c r="AT39" s="39"/>
-      <c r="AU39" s="39"/>
-      <c r="AV39" s="39"/>
-      <c r="AW39" s="39"/>
-      <c r="AX39" s="39"/>
-      <c r="AY39" s="39"/>
-      <c r="AZ39" s="39"/>
-      <c r="BA39" s="39"/>
-      <c r="BB39" s="39"/>
-      <c r="BC39" s="39"/>
-      <c r="BD39" s="39"/>
-      <c r="BE39" s="39"/>
-      <c r="BF39" s="39"/>
-      <c r="BG39" s="39"/>
-      <c r="BH39" s="39"/>
-      <c r="BI39" s="39"/>
-      <c r="BJ39" s="39"/>
-      <c r="BK39" s="39"/>
-      <c r="BL39" s="39"/>
-      <c r="BM39" s="39"/>
-      <c r="BN39" s="39"/>
-      <c r="BO39" s="39"/>
-      <c r="BP39" s="40"/>
-    </row>
-    <row r="40" spans="1:68">
-      <c r="E40" s="48" t="s">
+      <c r="AQ39" s="109"/>
+      <c r="AR39" s="109"/>
+      <c r="AS39" s="109"/>
+      <c r="AT39" s="109"/>
+      <c r="AU39" s="109"/>
+      <c r="AV39" s="109"/>
+      <c r="AW39" s="109"/>
+      <c r="AX39" s="109"/>
+      <c r="AY39" s="109"/>
+      <c r="AZ39" s="109"/>
+      <c r="BA39" s="109"/>
+      <c r="BB39" s="109"/>
+      <c r="BC39" s="109"/>
+      <c r="BD39" s="109"/>
+      <c r="BE39" s="109"/>
+      <c r="BF39" s="109"/>
+      <c r="BG39" s="109"/>
+      <c r="BH39" s="109"/>
+      <c r="BI39" s="109"/>
+      <c r="BJ39" s="109"/>
+      <c r="BK39" s="109"/>
+      <c r="BL39" s="109"/>
+      <c r="BM39" s="109"/>
+      <c r="BN39" s="109"/>
+      <c r="BO39" s="109"/>
+      <c r="BP39" s="114"/>
+    </row>
+    <row r="40" spans="1:68" ht="15">
+      <c r="E40" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="49"/>
-      <c r="N40" s="49"/>
-      <c r="O40" s="49"/>
-      <c r="P40" s="49"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="39" t="s">
+      <c r="F40" s="111"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="111"/>
+      <c r="I40" s="111"/>
+      <c r="J40" s="111"/>
+      <c r="K40" s="111"/>
+      <c r="L40" s="111"/>
+      <c r="M40" s="111"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="111"/>
+      <c r="P40" s="111"/>
+      <c r="Q40" s="111"/>
+      <c r="R40" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="S40" s="39"/>
-      <c r="T40" s="39"/>
-      <c r="U40" s="39"/>
-      <c r="V40" s="39"/>
-      <c r="W40" s="39"/>
-      <c r="X40" s="39"/>
-      <c r="Y40" s="39"/>
-      <c r="Z40" s="39"/>
-      <c r="AA40" s="39"/>
-      <c r="AB40" s="39"/>
-      <c r="AC40" s="39"/>
-      <c r="AD40" s="39"/>
-      <c r="AE40" s="39"/>
-      <c r="AF40" s="39"/>
-      <c r="AG40" s="39"/>
-      <c r="AH40" s="39"/>
-      <c r="AI40" s="39"/>
-      <c r="AJ40" s="39"/>
-      <c r="AK40" s="39"/>
-      <c r="AL40" s="39"/>
-      <c r="AM40" s="39"/>
-      <c r="AN40" s="39"/>
-      <c r="AO40" s="39"/>
-      <c r="AP40" s="39" t="s">
+      <c r="S40" s="109"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="109"/>
+      <c r="Y40" s="109"/>
+      <c r="Z40" s="109"/>
+      <c r="AA40" s="109"/>
+      <c r="AB40" s="109"/>
+      <c r="AC40" s="109"/>
+      <c r="AD40" s="109"/>
+      <c r="AE40" s="109"/>
+      <c r="AF40" s="109"/>
+      <c r="AG40" s="109"/>
+      <c r="AH40" s="109"/>
+      <c r="AI40" s="109"/>
+      <c r="AJ40" s="109"/>
+      <c r="AK40" s="109"/>
+      <c r="AL40" s="109"/>
+      <c r="AM40" s="109"/>
+      <c r="AN40" s="109"/>
+      <c r="AO40" s="109"/>
+      <c r="AP40" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="AQ40" s="39"/>
-      <c r="AR40" s="39"/>
-      <c r="AS40" s="39"/>
-      <c r="AT40" s="39"/>
-      <c r="AU40" s="39"/>
-      <c r="AV40" s="39"/>
-      <c r="AW40" s="39"/>
-      <c r="AX40" s="39"/>
-      <c r="AY40" s="39"/>
-      <c r="AZ40" s="39"/>
-      <c r="BA40" s="39"/>
-      <c r="BB40" s="39"/>
-      <c r="BC40" s="39"/>
-      <c r="BD40" s="39"/>
-      <c r="BE40" s="39"/>
-      <c r="BF40" s="39"/>
-      <c r="BG40" s="39"/>
-      <c r="BH40" s="39"/>
-      <c r="BI40" s="39"/>
-      <c r="BJ40" s="39"/>
-      <c r="BK40" s="39"/>
-      <c r="BL40" s="39"/>
-      <c r="BM40" s="39"/>
-      <c r="BN40" s="39"/>
-      <c r="BO40" s="39"/>
-      <c r="BP40" s="40"/>
-    </row>
-    <row r="41" spans="1:68">
-      <c r="E41" s="48" t="s">
+      <c r="AQ40" s="109"/>
+      <c r="AR40" s="109"/>
+      <c r="AS40" s="109"/>
+      <c r="AT40" s="109"/>
+      <c r="AU40" s="109"/>
+      <c r="AV40" s="109"/>
+      <c r="AW40" s="109"/>
+      <c r="AX40" s="109"/>
+      <c r="AY40" s="109"/>
+      <c r="AZ40" s="109"/>
+      <c r="BA40" s="109"/>
+      <c r="BB40" s="109"/>
+      <c r="BC40" s="109"/>
+      <c r="BD40" s="109"/>
+      <c r="BE40" s="109"/>
+      <c r="BF40" s="109"/>
+      <c r="BG40" s="109"/>
+      <c r="BH40" s="109"/>
+      <c r="BI40" s="109"/>
+      <c r="BJ40" s="109"/>
+      <c r="BK40" s="109"/>
+      <c r="BL40" s="109"/>
+      <c r="BM40" s="109"/>
+      <c r="BN40" s="109"/>
+      <c r="BO40" s="109"/>
+      <c r="BP40" s="114"/>
+    </row>
+    <row r="41" spans="1:68" ht="15">
+      <c r="E41" s="110" t="s">
         <v>73</v>
       </c>
-      <c r="F41" s="49"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
-      <c r="L41" s="49"/>
-      <c r="M41" s="49"/>
-      <c r="N41" s="49"/>
-      <c r="O41" s="49"/>
-      <c r="P41" s="49"/>
-      <c r="Q41" s="49"/>
-      <c r="R41" s="39" t="s">
+      <c r="F41" s="111"/>
+      <c r="G41" s="111"/>
+      <c r="H41" s="111"/>
+      <c r="I41" s="111"/>
+      <c r="J41" s="111"/>
+      <c r="K41" s="111"/>
+      <c r="L41" s="111"/>
+      <c r="M41" s="111"/>
+      <c r="N41" s="111"/>
+      <c r="O41" s="111"/>
+      <c r="P41" s="111"/>
+      <c r="Q41" s="111"/>
+      <c r="R41" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="S41" s="39"/>
-      <c r="T41" s="39"/>
-      <c r="U41" s="39"/>
-      <c r="V41" s="39"/>
-      <c r="W41" s="39"/>
-      <c r="X41" s="39"/>
-      <c r="Y41" s="39"/>
-      <c r="Z41" s="39"/>
-      <c r="AA41" s="39"/>
-      <c r="AB41" s="39"/>
-      <c r="AC41" s="39"/>
-      <c r="AD41" s="39"/>
-      <c r="AE41" s="39"/>
-      <c r="AF41" s="39"/>
-      <c r="AG41" s="39"/>
-      <c r="AH41" s="39"/>
-      <c r="AI41" s="39"/>
-      <c r="AJ41" s="39"/>
-      <c r="AK41" s="39"/>
-      <c r="AL41" s="39"/>
-      <c r="AM41" s="39"/>
-      <c r="AN41" s="39"/>
-      <c r="AO41" s="39"/>
-      <c r="AP41" s="39" t="s">
+      <c r="S41" s="109"/>
+      <c r="T41" s="109"/>
+      <c r="U41" s="109"/>
+      <c r="V41" s="109"/>
+      <c r="W41" s="109"/>
+      <c r="X41" s="109"/>
+      <c r="Y41" s="109"/>
+      <c r="Z41" s="109"/>
+      <c r="AA41" s="109"/>
+      <c r="AB41" s="109"/>
+      <c r="AC41" s="109"/>
+      <c r="AD41" s="109"/>
+      <c r="AE41" s="109"/>
+      <c r="AF41" s="109"/>
+      <c r="AG41" s="109"/>
+      <c r="AH41" s="109"/>
+      <c r="AI41" s="109"/>
+      <c r="AJ41" s="109"/>
+      <c r="AK41" s="109"/>
+      <c r="AL41" s="109"/>
+      <c r="AM41" s="109"/>
+      <c r="AN41" s="109"/>
+      <c r="AO41" s="109"/>
+      <c r="AP41" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="AQ41" s="39"/>
-      <c r="AR41" s="39"/>
-      <c r="AS41" s="39"/>
-      <c r="AT41" s="39"/>
-      <c r="AU41" s="39"/>
-      <c r="AV41" s="39"/>
-      <c r="AW41" s="39"/>
-      <c r="AX41" s="39"/>
-      <c r="AY41" s="39"/>
-      <c r="AZ41" s="39"/>
-      <c r="BA41" s="39"/>
-      <c r="BB41" s="39"/>
-      <c r="BC41" s="39"/>
-      <c r="BD41" s="39"/>
-      <c r="BE41" s="39"/>
-      <c r="BF41" s="39"/>
-      <c r="BG41" s="39"/>
-      <c r="BH41" s="39"/>
-      <c r="BI41" s="39"/>
-      <c r="BJ41" s="39"/>
-      <c r="BK41" s="39"/>
-      <c r="BL41" s="39"/>
-      <c r="BM41" s="39"/>
-      <c r="BN41" s="39"/>
-      <c r="BO41" s="39"/>
-      <c r="BP41" s="40"/>
-    </row>
-    <row r="42" spans="1:68">
-      <c r="E42" s="48" t="s">
+      <c r="AQ41" s="109"/>
+      <c r="AR41" s="109"/>
+      <c r="AS41" s="109"/>
+      <c r="AT41" s="109"/>
+      <c r="AU41" s="109"/>
+      <c r="AV41" s="109"/>
+      <c r="AW41" s="109"/>
+      <c r="AX41" s="109"/>
+      <c r="AY41" s="109"/>
+      <c r="AZ41" s="109"/>
+      <c r="BA41" s="109"/>
+      <c r="BB41" s="109"/>
+      <c r="BC41" s="109"/>
+      <c r="BD41" s="109"/>
+      <c r="BE41" s="109"/>
+      <c r="BF41" s="109"/>
+      <c r="BG41" s="109"/>
+      <c r="BH41" s="109"/>
+      <c r="BI41" s="109"/>
+      <c r="BJ41" s="109"/>
+      <c r="BK41" s="109"/>
+      <c r="BL41" s="109"/>
+      <c r="BM41" s="109"/>
+      <c r="BN41" s="109"/>
+      <c r="BO41" s="109"/>
+      <c r="BP41" s="114"/>
+    </row>
+    <row r="42" spans="1:68" ht="15">
+      <c r="E42" s="110" t="s">
         <v>76</v>
       </c>
-      <c r="F42" s="49"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="49"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="49"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="49"/>
-      <c r="O42" s="49"/>
-      <c r="P42" s="49"/>
-      <c r="Q42" s="49"/>
-      <c r="R42" s="39" t="s">
+      <c r="F42" s="111"/>
+      <c r="G42" s="111"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="111"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="111"/>
+      <c r="L42" s="111"/>
+      <c r="M42" s="111"/>
+      <c r="N42" s="111"/>
+      <c r="O42" s="111"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="S42" s="39"/>
-      <c r="T42" s="39"/>
-      <c r="U42" s="39"/>
-      <c r="V42" s="39"/>
-      <c r="W42" s="39"/>
-      <c r="X42" s="39"/>
-      <c r="Y42" s="39"/>
-      <c r="Z42" s="39"/>
-      <c r="AA42" s="39"/>
-      <c r="AB42" s="39"/>
-      <c r="AC42" s="39"/>
-      <c r="AD42" s="39"/>
-      <c r="AE42" s="39"/>
-      <c r="AF42" s="39"/>
-      <c r="AG42" s="39"/>
-      <c r="AH42" s="39"/>
-      <c r="AI42" s="39"/>
-      <c r="AJ42" s="39"/>
-      <c r="AK42" s="39"/>
-      <c r="AL42" s="39"/>
-      <c r="AM42" s="39"/>
-      <c r="AN42" s="39"/>
-      <c r="AO42" s="39"/>
-      <c r="AP42" s="39" t="s">
+      <c r="S42" s="109"/>
+      <c r="T42" s="109"/>
+      <c r="U42" s="109"/>
+      <c r="V42" s="109"/>
+      <c r="W42" s="109"/>
+      <c r="X42" s="109"/>
+      <c r="Y42" s="109"/>
+      <c r="Z42" s="109"/>
+      <c r="AA42" s="109"/>
+      <c r="AB42" s="109"/>
+      <c r="AC42" s="109"/>
+      <c r="AD42" s="109"/>
+      <c r="AE42" s="109"/>
+      <c r="AF42" s="109"/>
+      <c r="AG42" s="109"/>
+      <c r="AH42" s="109"/>
+      <c r="AI42" s="109"/>
+      <c r="AJ42" s="109"/>
+      <c r="AK42" s="109"/>
+      <c r="AL42" s="109"/>
+      <c r="AM42" s="109"/>
+      <c r="AN42" s="109"/>
+      <c r="AO42" s="109"/>
+      <c r="AP42" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="AQ42" s="39"/>
-      <c r="AR42" s="39"/>
-      <c r="AS42" s="39"/>
-      <c r="AT42" s="39"/>
-      <c r="AU42" s="39"/>
-      <c r="AV42" s="39"/>
-      <c r="AW42" s="39"/>
-      <c r="AX42" s="39"/>
-      <c r="AY42" s="39"/>
-      <c r="AZ42" s="39"/>
-      <c r="BA42" s="39"/>
-      <c r="BB42" s="39"/>
-      <c r="BC42" s="39"/>
-      <c r="BD42" s="39"/>
-      <c r="BE42" s="39"/>
-      <c r="BF42" s="39"/>
-      <c r="BG42" s="39"/>
-      <c r="BH42" s="39"/>
-      <c r="BI42" s="39"/>
-      <c r="BJ42" s="39"/>
-      <c r="BK42" s="39"/>
-      <c r="BL42" s="39"/>
-      <c r="BM42" s="39"/>
-      <c r="BN42" s="39"/>
-      <c r="BO42" s="39"/>
-      <c r="BP42" s="40"/>
-    </row>
-    <row r="43" spans="1:68">
-      <c r="E43" s="48" t="s">
+      <c r="AQ42" s="109"/>
+      <c r="AR42" s="109"/>
+      <c r="AS42" s="109"/>
+      <c r="AT42" s="109"/>
+      <c r="AU42" s="109"/>
+      <c r="AV42" s="109"/>
+      <c r="AW42" s="109"/>
+      <c r="AX42" s="109"/>
+      <c r="AY42" s="109"/>
+      <c r="AZ42" s="109"/>
+      <c r="BA42" s="109"/>
+      <c r="BB42" s="109"/>
+      <c r="BC42" s="109"/>
+      <c r="BD42" s="109"/>
+      <c r="BE42" s="109"/>
+      <c r="BF42" s="109"/>
+      <c r="BG42" s="109"/>
+      <c r="BH42" s="109"/>
+      <c r="BI42" s="109"/>
+      <c r="BJ42" s="109"/>
+      <c r="BK42" s="109"/>
+      <c r="BL42" s="109"/>
+      <c r="BM42" s="109"/>
+      <c r="BN42" s="109"/>
+      <c r="BO42" s="109"/>
+      <c r="BP42" s="114"/>
+    </row>
+    <row r="43" spans="1:68" ht="15">
+      <c r="E43" s="110" t="s">
         <v>79</v>
       </c>
-      <c r="F43" s="49"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="49"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="49"/>
-      <c r="O43" s="49"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="49"/>
-      <c r="R43" s="39" t="s">
+      <c r="F43" s="111"/>
+      <c r="G43" s="111"/>
+      <c r="H43" s="111"/>
+      <c r="I43" s="111"/>
+      <c r="J43" s="111"/>
+      <c r="K43" s="111"/>
+      <c r="L43" s="111"/>
+      <c r="M43" s="111"/>
+      <c r="N43" s="111"/>
+      <c r="O43" s="111"/>
+      <c r="P43" s="111"/>
+      <c r="Q43" s="111"/>
+      <c r="R43" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="S43" s="39"/>
-      <c r="T43" s="39"/>
-      <c r="U43" s="39"/>
-      <c r="V43" s="39"/>
-      <c r="W43" s="39"/>
-      <c r="X43" s="39"/>
-      <c r="Y43" s="39"/>
-      <c r="Z43" s="39"/>
-      <c r="AA43" s="39"/>
-      <c r="AB43" s="39"/>
-      <c r="AC43" s="39"/>
-      <c r="AD43" s="39"/>
-      <c r="AE43" s="39"/>
-      <c r="AF43" s="39"/>
-      <c r="AG43" s="39"/>
-      <c r="AH43" s="39"/>
-      <c r="AI43" s="39"/>
-      <c r="AJ43" s="39"/>
-      <c r="AK43" s="39"/>
-      <c r="AL43" s="39"/>
-      <c r="AM43" s="39"/>
-      <c r="AN43" s="39"/>
-      <c r="AO43" s="39"/>
-      <c r="AP43" s="39" t="s">
+      <c r="S43" s="109"/>
+      <c r="T43" s="109"/>
+      <c r="U43" s="109"/>
+      <c r="V43" s="109"/>
+      <c r="W43" s="109"/>
+      <c r="X43" s="109"/>
+      <c r="Y43" s="109"/>
+      <c r="Z43" s="109"/>
+      <c r="AA43" s="109"/>
+      <c r="AB43" s="109"/>
+      <c r="AC43" s="109"/>
+      <c r="AD43" s="109"/>
+      <c r="AE43" s="109"/>
+      <c r="AF43" s="109"/>
+      <c r="AG43" s="109"/>
+      <c r="AH43" s="109"/>
+      <c r="AI43" s="109"/>
+      <c r="AJ43" s="109"/>
+      <c r="AK43" s="109"/>
+      <c r="AL43" s="109"/>
+      <c r="AM43" s="109"/>
+      <c r="AN43" s="109"/>
+      <c r="AO43" s="109"/>
+      <c r="AP43" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="AQ43" s="39"/>
-      <c r="AR43" s="39"/>
-      <c r="AS43" s="39"/>
-      <c r="AT43" s="39"/>
-      <c r="AU43" s="39"/>
-      <c r="AV43" s="39"/>
-      <c r="AW43" s="39"/>
-      <c r="AX43" s="39"/>
-      <c r="AY43" s="39"/>
-      <c r="AZ43" s="39"/>
-      <c r="BA43" s="39"/>
-      <c r="BB43" s="39"/>
-      <c r="BC43" s="39"/>
-      <c r="BD43" s="39"/>
-      <c r="BE43" s="39"/>
-      <c r="BF43" s="39"/>
-      <c r="BG43" s="39"/>
-      <c r="BH43" s="39"/>
-      <c r="BI43" s="39"/>
-      <c r="BJ43" s="39"/>
-      <c r="BK43" s="39"/>
-      <c r="BL43" s="39"/>
-      <c r="BM43" s="39"/>
-      <c r="BN43" s="39"/>
-      <c r="BO43" s="39"/>
-      <c r="BP43" s="40"/>
-    </row>
-    <row r="44" spans="1:68" ht="14.4" thickBot="1">
-      <c r="E44" s="46" t="s">
+      <c r="AQ43" s="109"/>
+      <c r="AR43" s="109"/>
+      <c r="AS43" s="109"/>
+      <c r="AT43" s="109"/>
+      <c r="AU43" s="109"/>
+      <c r="AV43" s="109"/>
+      <c r="AW43" s="109"/>
+      <c r="AX43" s="109"/>
+      <c r="AY43" s="109"/>
+      <c r="AZ43" s="109"/>
+      <c r="BA43" s="109"/>
+      <c r="BB43" s="109"/>
+      <c r="BC43" s="109"/>
+      <c r="BD43" s="109"/>
+      <c r="BE43" s="109"/>
+      <c r="BF43" s="109"/>
+      <c r="BG43" s="109"/>
+      <c r="BH43" s="109"/>
+      <c r="BI43" s="109"/>
+      <c r="BJ43" s="109"/>
+      <c r="BK43" s="109"/>
+      <c r="BL43" s="109"/>
+      <c r="BM43" s="109"/>
+      <c r="BN43" s="109"/>
+      <c r="BO43" s="109"/>
+      <c r="BP43" s="114"/>
+    </row>
+    <row r="44" spans="1:68" ht="15.75" thickBot="1">
+      <c r="E44" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="47"/>
-      <c r="K44" s="47"/>
-      <c r="L44" s="47"/>
-      <c r="M44" s="47"/>
-      <c r="N44" s="47"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="47"/>
-      <c r="Q44" s="47"/>
-      <c r="R44" s="41" t="s">
+      <c r="F44" s="107"/>
+      <c r="G44" s="107"/>
+      <c r="H44" s="107"/>
+      <c r="I44" s="107"/>
+      <c r="J44" s="107"/>
+      <c r="K44" s="107"/>
+      <c r="L44" s="107"/>
+      <c r="M44" s="107"/>
+      <c r="N44" s="107"/>
+      <c r="O44" s="107"/>
+      <c r="P44" s="107"/>
+      <c r="Q44" s="107"/>
+      <c r="R44" s="112" t="s">
         <v>83</v>
       </c>
-      <c r="S44" s="41"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="41"/>
-      <c r="V44" s="41"/>
-      <c r="W44" s="41"/>
-      <c r="X44" s="41"/>
-      <c r="Y44" s="41"/>
-      <c r="Z44" s="41"/>
-      <c r="AA44" s="41"/>
-      <c r="AB44" s="41"/>
-      <c r="AC44" s="41"/>
-      <c r="AD44" s="41"/>
-      <c r="AE44" s="41"/>
-      <c r="AF44" s="41"/>
-      <c r="AG44" s="41"/>
-      <c r="AH44" s="41"/>
-      <c r="AI44" s="41"/>
-      <c r="AJ44" s="41"/>
-      <c r="AK44" s="41"/>
-      <c r="AL44" s="41"/>
-      <c r="AM44" s="41"/>
-      <c r="AN44" s="41"/>
-      <c r="AO44" s="41"/>
-      <c r="AP44" s="41" t="s">
+      <c r="S44" s="112"/>
+      <c r="T44" s="112"/>
+      <c r="U44" s="112"/>
+      <c r="V44" s="112"/>
+      <c r="W44" s="112"/>
+      <c r="X44" s="112"/>
+      <c r="Y44" s="112"/>
+      <c r="Z44" s="112"/>
+      <c r="AA44" s="112"/>
+      <c r="AB44" s="112"/>
+      <c r="AC44" s="112"/>
+      <c r="AD44" s="112"/>
+      <c r="AE44" s="112"/>
+      <c r="AF44" s="112"/>
+      <c r="AG44" s="112"/>
+      <c r="AH44" s="112"/>
+      <c r="AI44" s="112"/>
+      <c r="AJ44" s="112"/>
+      <c r="AK44" s="112"/>
+      <c r="AL44" s="112"/>
+      <c r="AM44" s="112"/>
+      <c r="AN44" s="112"/>
+      <c r="AO44" s="112"/>
+      <c r="AP44" s="112" t="s">
         <v>84</v>
       </c>
-      <c r="AQ44" s="41"/>
-      <c r="AR44" s="41"/>
-      <c r="AS44" s="41"/>
-      <c r="AT44" s="41"/>
-      <c r="AU44" s="41"/>
-      <c r="AV44" s="41"/>
-      <c r="AW44" s="41"/>
-      <c r="AX44" s="41"/>
-      <c r="AY44" s="41"/>
-      <c r="AZ44" s="41"/>
-      <c r="BA44" s="41"/>
-      <c r="BB44" s="41"/>
-      <c r="BC44" s="41"/>
-      <c r="BD44" s="41"/>
-      <c r="BE44" s="41"/>
-      <c r="BF44" s="41"/>
-      <c r="BG44" s="41"/>
-      <c r="BH44" s="41"/>
-      <c r="BI44" s="41"/>
-      <c r="BJ44" s="41"/>
-      <c r="BK44" s="41"/>
-      <c r="BL44" s="41"/>
-      <c r="BM44" s="41"/>
-      <c r="BN44" s="41"/>
-      <c r="BO44" s="41"/>
-      <c r="BP44" s="42"/>
-    </row>
-    <row r="45" spans="1:68" ht="14.4" thickBot="1"/>
-    <row r="46" spans="1:68" s="16" customFormat="1" ht="14.4" thickBot="1">
+      <c r="AQ44" s="112"/>
+      <c r="AR44" s="112"/>
+      <c r="AS44" s="112"/>
+      <c r="AT44" s="112"/>
+      <c r="AU44" s="112"/>
+      <c r="AV44" s="112"/>
+      <c r="AW44" s="112"/>
+      <c r="AX44" s="112"/>
+      <c r="AY44" s="112"/>
+      <c r="AZ44" s="112"/>
+      <c r="BA44" s="112"/>
+      <c r="BB44" s="112"/>
+      <c r="BC44" s="112"/>
+      <c r="BD44" s="112"/>
+      <c r="BE44" s="112"/>
+      <c r="BF44" s="112"/>
+      <c r="BG44" s="112"/>
+      <c r="BH44" s="112"/>
+      <c r="BI44" s="112"/>
+      <c r="BJ44" s="112"/>
+      <c r="BK44" s="112"/>
+      <c r="BL44" s="112"/>
+      <c r="BM44" s="112"/>
+      <c r="BN44" s="112"/>
+      <c r="BO44" s="112"/>
+      <c r="BP44" s="115"/>
+    </row>
+    <row r="45" spans="1:68" ht="15" thickBot="1"/>
+    <row r="46" spans="1:68" s="16" customFormat="1" ht="15.75" thickBot="1">
       <c r="A46" s="15"/>
       <c r="C46" s="17" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:68" ht="14.4" thickBot="1"/>
-    <row r="48" spans="1:68" ht="17.399999999999999">
+    <row r="47" spans="1:68" ht="15" thickBot="1"/>
+    <row r="48" spans="1:68" ht="17.25">
       <c r="E48" s="18" t="s">
         <v>114</v>
       </c>
@@ -6013,35 +6010,35 @@
       <c r="U48" s="19"/>
       <c r="V48" s="19"/>
       <c r="W48" s="20"/>
-      <c r="Z48" s="66" t="s">
+      <c r="Z48" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="AA48" s="67"/>
-      <c r="AB48" s="67"/>
-      <c r="AC48" s="67"/>
-      <c r="AD48" s="67"/>
-      <c r="AE48" s="67"/>
-      <c r="AF48" s="67"/>
-      <c r="AG48" s="67"/>
-      <c r="AH48" s="67"/>
-      <c r="AI48" s="67"/>
-      <c r="AJ48" s="67"/>
-      <c r="AK48" s="67"/>
-      <c r="AL48" s="67"/>
-      <c r="AM48" s="67"/>
-      <c r="AN48" s="67"/>
-      <c r="AO48" s="67"/>
-      <c r="AP48" s="67"/>
-      <c r="AQ48" s="67"/>
-      <c r="AR48" s="67"/>
-      <c r="AS48" s="67"/>
-      <c r="AT48" s="67"/>
-      <c r="AU48" s="67"/>
-      <c r="AV48" s="67"/>
-      <c r="AW48" s="67"/>
-      <c r="AX48" s="68"/>
-    </row>
-    <row r="49" spans="5:50">
+      <c r="AA48" s="36"/>
+      <c r="AB48" s="36"/>
+      <c r="AC48" s="36"/>
+      <c r="AD48" s="36"/>
+      <c r="AE48" s="36"/>
+      <c r="AF48" s="36"/>
+      <c r="AG48" s="36"/>
+      <c r="AH48" s="36"/>
+      <c r="AI48" s="36"/>
+      <c r="AJ48" s="36"/>
+      <c r="AK48" s="36"/>
+      <c r="AL48" s="36"/>
+      <c r="AM48" s="36"/>
+      <c r="AN48" s="36"/>
+      <c r="AO48" s="36"/>
+      <c r="AP48" s="36"/>
+      <c r="AQ48" s="36"/>
+      <c r="AR48" s="36"/>
+      <c r="AS48" s="36"/>
+      <c r="AT48" s="36"/>
+      <c r="AU48" s="36"/>
+      <c r="AV48" s="36"/>
+      <c r="AW48" s="36"/>
+      <c r="AX48" s="37"/>
+    </row>
+    <row r="49" spans="5:50" ht="15">
       <c r="E49" s="21" t="s">
         <v>115</v>
       </c>
@@ -6063,33 +6060,33 @@
       <c r="U49" s="22"/>
       <c r="V49" s="22"/>
       <c r="W49" s="23"/>
-      <c r="Z49" s="69"/>
-      <c r="AA49" s="70" t="s">
+      <c r="Z49" s="38"/>
+      <c r="AA49" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="AB49" s="71"/>
-      <c r="AC49" s="71"/>
-      <c r="AD49" s="71"/>
-      <c r="AE49" s="71"/>
-      <c r="AF49" s="71"/>
-      <c r="AG49" s="71"/>
-      <c r="AH49" s="71"/>
-      <c r="AI49" s="71"/>
-      <c r="AJ49" s="71"/>
-      <c r="AK49" s="71"/>
-      <c r="AL49" s="71"/>
-      <c r="AM49" s="71"/>
-      <c r="AN49" s="71"/>
-      <c r="AO49" s="71"/>
-      <c r="AP49" s="71"/>
-      <c r="AQ49" s="71"/>
-      <c r="AR49" s="71"/>
-      <c r="AS49" s="71"/>
-      <c r="AT49" s="71"/>
-      <c r="AU49" s="71"/>
-      <c r="AV49" s="71"/>
-      <c r="AW49" s="71"/>
-      <c r="AX49" s="72"/>
+      <c r="AB49" s="40"/>
+      <c r="AC49" s="40"/>
+      <c r="AD49" s="40"/>
+      <c r="AE49" s="40"/>
+      <c r="AF49" s="40"/>
+      <c r="AG49" s="40"/>
+      <c r="AH49" s="40"/>
+      <c r="AI49" s="40"/>
+      <c r="AJ49" s="40"/>
+      <c r="AK49" s="40"/>
+      <c r="AL49" s="40"/>
+      <c r="AM49" s="40"/>
+      <c r="AN49" s="40"/>
+      <c r="AO49" s="40"/>
+      <c r="AP49" s="40"/>
+      <c r="AQ49" s="40"/>
+      <c r="AR49" s="40"/>
+      <c r="AS49" s="40"/>
+      <c r="AT49" s="40"/>
+      <c r="AU49" s="40"/>
+      <c r="AV49" s="40"/>
+      <c r="AW49" s="40"/>
+      <c r="AX49" s="41"/>
     </row>
     <row r="50" spans="5:50">
       <c r="E50" s="24" t="s">
@@ -6113,33 +6110,33 @@
       <c r="U50" s="22"/>
       <c r="V50" s="22"/>
       <c r="W50" s="23"/>
-      <c r="Z50" s="69"/>
-      <c r="AA50" s="70" t="s">
+      <c r="Z50" s="38"/>
+      <c r="AA50" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="AB50" s="71"/>
-      <c r="AC50" s="71"/>
-      <c r="AD50" s="71"/>
-      <c r="AE50" s="71"/>
-      <c r="AF50" s="71"/>
-      <c r="AG50" s="71"/>
-      <c r="AH50" s="71"/>
-      <c r="AI50" s="71"/>
-      <c r="AJ50" s="71"/>
-      <c r="AK50" s="71"/>
-      <c r="AL50" s="71"/>
-      <c r="AM50" s="71"/>
-      <c r="AN50" s="71"/>
-      <c r="AO50" s="71"/>
-      <c r="AP50" s="71"/>
-      <c r="AQ50" s="71"/>
-      <c r="AR50" s="71"/>
-      <c r="AS50" s="71"/>
-      <c r="AT50" s="71"/>
-      <c r="AU50" s="71"/>
-      <c r="AV50" s="71"/>
-      <c r="AW50" s="71"/>
-      <c r="AX50" s="72"/>
+      <c r="AB50" s="40"/>
+      <c r="AC50" s="40"/>
+      <c r="AD50" s="40"/>
+      <c r="AE50" s="40"/>
+      <c r="AF50" s="40"/>
+      <c r="AG50" s="40"/>
+      <c r="AH50" s="40"/>
+      <c r="AI50" s="40"/>
+      <c r="AJ50" s="40"/>
+      <c r="AK50" s="40"/>
+      <c r="AL50" s="40"/>
+      <c r="AM50" s="40"/>
+      <c r="AN50" s="40"/>
+      <c r="AO50" s="40"/>
+      <c r="AP50" s="40"/>
+      <c r="AQ50" s="40"/>
+      <c r="AR50" s="40"/>
+      <c r="AS50" s="40"/>
+      <c r="AT50" s="40"/>
+      <c r="AU50" s="40"/>
+      <c r="AV50" s="40"/>
+      <c r="AW50" s="40"/>
+      <c r="AX50" s="41"/>
     </row>
     <row r="51" spans="5:50">
       <c r="E51" s="24" t="s">
@@ -6163,35 +6160,35 @@
       <c r="U51" s="22"/>
       <c r="V51" s="22"/>
       <c r="W51" s="23"/>
-      <c r="Z51" s="69" t="s">
+      <c r="Z51" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="AA51" s="71"/>
-      <c r="AB51" s="71"/>
-      <c r="AC51" s="71"/>
-      <c r="AD51" s="71"/>
-      <c r="AE51" s="71"/>
-      <c r="AF51" s="71"/>
-      <c r="AG51" s="71"/>
-      <c r="AH51" s="71"/>
-      <c r="AI51" s="71"/>
-      <c r="AJ51" s="71"/>
-      <c r="AK51" s="71"/>
-      <c r="AL51" s="71"/>
-      <c r="AM51" s="71"/>
-      <c r="AN51" s="71"/>
-      <c r="AO51" s="71"/>
-      <c r="AP51" s="71"/>
-      <c r="AQ51" s="71"/>
-      <c r="AR51" s="71"/>
-      <c r="AS51" s="71"/>
-      <c r="AT51" s="71"/>
-      <c r="AU51" s="71"/>
-      <c r="AV51" s="71"/>
-      <c r="AW51" s="71"/>
-      <c r="AX51" s="72"/>
-    </row>
-    <row r="52" spans="5:50">
+      <c r="AA51" s="40"/>
+      <c r="AB51" s="40"/>
+      <c r="AC51" s="40"/>
+      <c r="AD51" s="40"/>
+      <c r="AE51" s="40"/>
+      <c r="AF51" s="40"/>
+      <c r="AG51" s="40"/>
+      <c r="AH51" s="40"/>
+      <c r="AI51" s="40"/>
+      <c r="AJ51" s="40"/>
+      <c r="AK51" s="40"/>
+      <c r="AL51" s="40"/>
+      <c r="AM51" s="40"/>
+      <c r="AN51" s="40"/>
+      <c r="AO51" s="40"/>
+      <c r="AP51" s="40"/>
+      <c r="AQ51" s="40"/>
+      <c r="AR51" s="40"/>
+      <c r="AS51" s="40"/>
+      <c r="AT51" s="40"/>
+      <c r="AU51" s="40"/>
+      <c r="AV51" s="40"/>
+      <c r="AW51" s="40"/>
+      <c r="AX51" s="41"/>
+    </row>
+    <row r="52" spans="5:50" ht="15">
       <c r="E52" s="21" t="s">
         <v>118</v>
       </c>
@@ -6213,33 +6210,33 @@
       <c r="U52" s="22"/>
       <c r="V52" s="22"/>
       <c r="W52" s="23"/>
-      <c r="Z52" s="69"/>
-      <c r="AA52" s="70" t="s">
+      <c r="Z52" s="38"/>
+      <c r="AA52" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AB52" s="71"/>
-      <c r="AC52" s="71"/>
-      <c r="AD52" s="71"/>
-      <c r="AE52" s="71"/>
-      <c r="AF52" s="71"/>
-      <c r="AG52" s="71"/>
-      <c r="AH52" s="71"/>
-      <c r="AI52" s="71"/>
-      <c r="AJ52" s="71"/>
-      <c r="AK52" s="71"/>
-      <c r="AL52" s="71"/>
-      <c r="AM52" s="71"/>
-      <c r="AN52" s="71"/>
-      <c r="AO52" s="71"/>
-      <c r="AP52" s="71"/>
-      <c r="AQ52" s="71"/>
-      <c r="AR52" s="71"/>
-      <c r="AS52" s="71"/>
-      <c r="AT52" s="71"/>
-      <c r="AU52" s="71"/>
-      <c r="AV52" s="71"/>
-      <c r="AW52" s="71"/>
-      <c r="AX52" s="72"/>
+      <c r="AB52" s="40"/>
+      <c r="AC52" s="40"/>
+      <c r="AD52" s="40"/>
+      <c r="AE52" s="40"/>
+      <c r="AF52" s="40"/>
+      <c r="AG52" s="40"/>
+      <c r="AH52" s="40"/>
+      <c r="AI52" s="40"/>
+      <c r="AJ52" s="40"/>
+      <c r="AK52" s="40"/>
+      <c r="AL52" s="40"/>
+      <c r="AM52" s="40"/>
+      <c r="AN52" s="40"/>
+      <c r="AO52" s="40"/>
+      <c r="AP52" s="40"/>
+      <c r="AQ52" s="40"/>
+      <c r="AR52" s="40"/>
+      <c r="AS52" s="40"/>
+      <c r="AT52" s="40"/>
+      <c r="AU52" s="40"/>
+      <c r="AV52" s="40"/>
+      <c r="AW52" s="40"/>
+      <c r="AX52" s="41"/>
     </row>
     <row r="53" spans="5:50">
       <c r="E53" s="25" t="s">
@@ -6263,33 +6260,33 @@
       <c r="U53" s="22"/>
       <c r="V53" s="22"/>
       <c r="W53" s="23"/>
-      <c r="Z53" s="69"/>
-      <c r="AA53" s="70" t="s">
+      <c r="Z53" s="38"/>
+      <c r="AA53" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="AB53" s="71"/>
-      <c r="AC53" s="71"/>
-      <c r="AD53" s="71"/>
-      <c r="AE53" s="71"/>
-      <c r="AF53" s="71"/>
-      <c r="AG53" s="71"/>
-      <c r="AH53" s="71"/>
-      <c r="AI53" s="71"/>
-      <c r="AJ53" s="71"/>
-      <c r="AK53" s="71"/>
-      <c r="AL53" s="71"/>
-      <c r="AM53" s="71"/>
-      <c r="AN53" s="71"/>
-      <c r="AO53" s="71"/>
-      <c r="AP53" s="71"/>
-      <c r="AQ53" s="71"/>
-      <c r="AR53" s="71"/>
-      <c r="AS53" s="71"/>
-      <c r="AT53" s="71"/>
-      <c r="AU53" s="71"/>
-      <c r="AV53" s="71"/>
-      <c r="AW53" s="71"/>
-      <c r="AX53" s="72"/>
+      <c r="AB53" s="40"/>
+      <c r="AC53" s="40"/>
+      <c r="AD53" s="40"/>
+      <c r="AE53" s="40"/>
+      <c r="AF53" s="40"/>
+      <c r="AG53" s="40"/>
+      <c r="AH53" s="40"/>
+      <c r="AI53" s="40"/>
+      <c r="AJ53" s="40"/>
+      <c r="AK53" s="40"/>
+      <c r="AL53" s="40"/>
+      <c r="AM53" s="40"/>
+      <c r="AN53" s="40"/>
+      <c r="AO53" s="40"/>
+      <c r="AP53" s="40"/>
+      <c r="AQ53" s="40"/>
+      <c r="AR53" s="40"/>
+      <c r="AS53" s="40"/>
+      <c r="AT53" s="40"/>
+      <c r="AU53" s="40"/>
+      <c r="AV53" s="40"/>
+      <c r="AW53" s="40"/>
+      <c r="AX53" s="41"/>
     </row>
     <row r="54" spans="5:50">
       <c r="E54" s="25" t="s">
@@ -6313,33 +6310,33 @@
       <c r="U54" s="22"/>
       <c r="V54" s="22"/>
       <c r="W54" s="23"/>
-      <c r="Z54" s="69" t="s">
+      <c r="Z54" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="AA54" s="71"/>
-      <c r="AB54" s="71"/>
-      <c r="AC54" s="71"/>
-      <c r="AD54" s="71"/>
-      <c r="AE54" s="71"/>
-      <c r="AF54" s="71"/>
-      <c r="AG54" s="71"/>
-      <c r="AH54" s="71"/>
-      <c r="AI54" s="71"/>
-      <c r="AJ54" s="71"/>
-      <c r="AK54" s="71"/>
-      <c r="AL54" s="71"/>
-      <c r="AM54" s="71"/>
-      <c r="AN54" s="71"/>
-      <c r="AO54" s="71"/>
-      <c r="AP54" s="71"/>
-      <c r="AQ54" s="71"/>
-      <c r="AR54" s="71"/>
-      <c r="AS54" s="71"/>
-      <c r="AT54" s="71"/>
-      <c r="AU54" s="71"/>
-      <c r="AV54" s="71"/>
-      <c r="AW54" s="71"/>
-      <c r="AX54" s="72"/>
+      <c r="AA54" s="40"/>
+      <c r="AB54" s="40"/>
+      <c r="AC54" s="40"/>
+      <c r="AD54" s="40"/>
+      <c r="AE54" s="40"/>
+      <c r="AF54" s="40"/>
+      <c r="AG54" s="40"/>
+      <c r="AH54" s="40"/>
+      <c r="AI54" s="40"/>
+      <c r="AJ54" s="40"/>
+      <c r="AK54" s="40"/>
+      <c r="AL54" s="40"/>
+      <c r="AM54" s="40"/>
+      <c r="AN54" s="40"/>
+      <c r="AO54" s="40"/>
+      <c r="AP54" s="40"/>
+      <c r="AQ54" s="40"/>
+      <c r="AR54" s="40"/>
+      <c r="AS54" s="40"/>
+      <c r="AT54" s="40"/>
+      <c r="AU54" s="40"/>
+      <c r="AV54" s="40"/>
+      <c r="AW54" s="40"/>
+      <c r="AX54" s="41"/>
     </row>
     <row r="55" spans="5:50">
       <c r="E55" s="25" t="s">
@@ -6363,37 +6360,37 @@
       <c r="U55" s="22"/>
       <c r="V55" s="22"/>
       <c r="W55" s="23"/>
-      <c r="Z55" s="69"/>
-      <c r="AA55" s="70" t="s">
+      <c r="Z55" s="38"/>
+      <c r="AA55" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="AB55" s="71"/>
-      <c r="AC55" s="71"/>
-      <c r="AD55" s="71"/>
-      <c r="AE55" s="71"/>
-      <c r="AF55" s="71"/>
-      <c r="AG55" s="71"/>
-      <c r="AH55" s="71"/>
-      <c r="AI55" s="71"/>
-      <c r="AJ55" s="71"/>
-      <c r="AK55" s="71"/>
-      <c r="AL55" s="71"/>
-      <c r="AM55" s="71"/>
-      <c r="AN55" s="71"/>
-      <c r="AO55" s="71"/>
-      <c r="AP55" s="71"/>
-      <c r="AQ55" s="71"/>
-      <c r="AR55" s="71"/>
-      <c r="AS55" s="71"/>
-      <c r="AT55" s="71"/>
-      <c r="AU55" s="71" t="s">
+      <c r="AB55" s="40"/>
+      <c r="AC55" s="40"/>
+      <c r="AD55" s="40"/>
+      <c r="AE55" s="40"/>
+      <c r="AF55" s="40"/>
+      <c r="AG55" s="40"/>
+      <c r="AH55" s="40"/>
+      <c r="AI55" s="40"/>
+      <c r="AJ55" s="40"/>
+      <c r="AK55" s="40"/>
+      <c r="AL55" s="40"/>
+      <c r="AM55" s="40"/>
+      <c r="AN55" s="40"/>
+      <c r="AO55" s="40"/>
+      <c r="AP55" s="40"/>
+      <c r="AQ55" s="40"/>
+      <c r="AR55" s="40"/>
+      <c r="AS55" s="40"/>
+      <c r="AT55" s="40"/>
+      <c r="AU55" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="AV55" s="71"/>
-      <c r="AW55" s="71"/>
-      <c r="AX55" s="72"/>
-    </row>
-    <row r="56" spans="5:50" ht="14.4" thickBot="1">
+      <c r="AV55" s="40"/>
+      <c r="AW55" s="40"/>
+      <c r="AX55" s="41"/>
+    </row>
+    <row r="56" spans="5:50" ht="15" thickBot="1">
       <c r="E56" s="25" t="s">
         <v>119</v>
       </c>
@@ -6415,35 +6412,35 @@
       <c r="U56" s="22"/>
       <c r="V56" s="22"/>
       <c r="W56" s="23"/>
-      <c r="Z56" s="73"/>
-      <c r="AA56" s="74" t="s">
+      <c r="Z56" s="42"/>
+      <c r="AA56" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="AB56" s="75"/>
-      <c r="AC56" s="75"/>
-      <c r="AD56" s="75"/>
-      <c r="AE56" s="75"/>
-      <c r="AF56" s="75"/>
-      <c r="AG56" s="75"/>
-      <c r="AH56" s="75"/>
-      <c r="AI56" s="75"/>
-      <c r="AJ56" s="75"/>
-      <c r="AK56" s="75"/>
-      <c r="AL56" s="75"/>
-      <c r="AM56" s="75"/>
-      <c r="AN56" s="75"/>
-      <c r="AO56" s="75"/>
-      <c r="AP56" s="75"/>
-      <c r="AQ56" s="75"/>
-      <c r="AR56" s="75"/>
-      <c r="AS56" s="75"/>
-      <c r="AT56" s="75"/>
-      <c r="AU56" s="75"/>
-      <c r="AV56" s="75"/>
-      <c r="AW56" s="75"/>
-      <c r="AX56" s="76"/>
-    </row>
-    <row r="57" spans="5:50">
+      <c r="AB56" s="44"/>
+      <c r="AC56" s="44"/>
+      <c r="AD56" s="44"/>
+      <c r="AE56" s="44"/>
+      <c r="AF56" s="44"/>
+      <c r="AG56" s="44"/>
+      <c r="AH56" s="44"/>
+      <c r="AI56" s="44"/>
+      <c r="AJ56" s="44"/>
+      <c r="AK56" s="44"/>
+      <c r="AL56" s="44"/>
+      <c r="AM56" s="44"/>
+      <c r="AN56" s="44"/>
+      <c r="AO56" s="44"/>
+      <c r="AP56" s="44"/>
+      <c r="AQ56" s="44"/>
+      <c r="AR56" s="44"/>
+      <c r="AS56" s="44"/>
+      <c r="AT56" s="44"/>
+      <c r="AU56" s="44"/>
+      <c r="AV56" s="44"/>
+      <c r="AW56" s="44"/>
+      <c r="AX56" s="45"/>
+    </row>
+    <row r="57" spans="5:50" ht="15">
       <c r="E57" s="21" t="s">
         <v>120</v>
       </c>
@@ -6512,7 +6509,7 @@
       <c r="V59" s="22"/>
       <c r="W59" s="23"/>
     </row>
-    <row r="60" spans="5:50">
+    <row r="60" spans="5:50" ht="15">
       <c r="E60" s="21" t="s">
         <v>123</v>
       </c>
@@ -6558,7 +6555,7 @@
       <c r="V61" s="22"/>
       <c r="W61" s="23"/>
     </row>
-    <row r="62" spans="5:50">
+    <row r="62" spans="5:50" ht="15">
       <c r="E62" s="21" t="s">
         <v>125</v>
       </c>
@@ -6604,7 +6601,7 @@
       <c r="V63" s="22"/>
       <c r="W63" s="23"/>
     </row>
-    <row r="64" spans="5:50">
+    <row r="64" spans="5:50" ht="15">
       <c r="E64" s="21" t="s">
         <v>127</v>
       </c>
@@ -6650,7 +6647,7 @@
       <c r="V65" s="22"/>
       <c r="W65" s="23"/>
     </row>
-    <row r="66" spans="5:23">
+    <row r="66" spans="5:23" ht="15">
       <c r="E66" s="21" t="s">
         <v>129</v>
       </c>
@@ -6696,7 +6693,7 @@
       <c r="V67" s="22"/>
       <c r="W67" s="23"/>
     </row>
-    <row r="68" spans="5:23">
+    <row r="68" spans="5:23" ht="15">
       <c r="E68" s="21" t="s">
         <v>131</v>
       </c>
@@ -6742,7 +6739,7 @@
       <c r="V69" s="22"/>
       <c r="W69" s="23"/>
     </row>
-    <row r="70" spans="5:23">
+    <row r="70" spans="5:23" ht="15">
       <c r="E70" s="21" t="s">
         <v>133</v>
       </c>
@@ -6765,7 +6762,7 @@
       <c r="V70" s="22"/>
       <c r="W70" s="23"/>
     </row>
-    <row r="71" spans="5:23" ht="14.4" thickBot="1">
+    <row r="71" spans="5:23" ht="15" thickBot="1">
       <c r="E71" s="26" t="s">
         <v>134</v>
       </c>
@@ -6802,6 +6799,7 @@
     <mergeCell ref="L15:AG15"/>
     <mergeCell ref="L13:AG13"/>
     <mergeCell ref="L14:AG14"/>
+    <mergeCell ref="D27:H27"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
     <mergeCell ref="D30:H30"/>
@@ -6809,12 +6807,6 @@
     <mergeCell ref="I28:P28"/>
     <mergeCell ref="I29:P29"/>
     <mergeCell ref="I30:P30"/>
-    <mergeCell ref="E37:Q37"/>
-    <mergeCell ref="AZ12:BI12"/>
-    <mergeCell ref="AZ14:BI14"/>
-    <mergeCell ref="AZ13:BI13"/>
-    <mergeCell ref="AZ15:BI15"/>
-    <mergeCell ref="AQ27:BB27"/>
     <mergeCell ref="AQ28:BB28"/>
     <mergeCell ref="Q27:AC27"/>
     <mergeCell ref="Q28:AC28"/>
@@ -6824,41 +6816,46 @@
     <mergeCell ref="AD28:AP28"/>
     <mergeCell ref="AD29:AP29"/>
     <mergeCell ref="AD30:AP30"/>
-    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="AZ12:BI12"/>
+    <mergeCell ref="AZ14:BI14"/>
+    <mergeCell ref="AZ13:BI13"/>
+    <mergeCell ref="AZ15:BI15"/>
+    <mergeCell ref="AQ27:BB27"/>
     <mergeCell ref="AQ29:BB29"/>
     <mergeCell ref="AQ30:BB30"/>
     <mergeCell ref="E34:Q34"/>
     <mergeCell ref="E35:Q35"/>
     <mergeCell ref="E36:Q36"/>
+    <mergeCell ref="AP44:BP44"/>
+    <mergeCell ref="R38:AO38"/>
+    <mergeCell ref="R39:AO39"/>
+    <mergeCell ref="R40:AO40"/>
+    <mergeCell ref="R41:AO41"/>
+    <mergeCell ref="R42:AO42"/>
+    <mergeCell ref="AP39:BP39"/>
+    <mergeCell ref="AP40:BP40"/>
+    <mergeCell ref="AP41:BP41"/>
+    <mergeCell ref="AP42:BP42"/>
+    <mergeCell ref="AP43:BP43"/>
+    <mergeCell ref="AP34:BP34"/>
+    <mergeCell ref="AP35:BP35"/>
+    <mergeCell ref="AP36:BP36"/>
+    <mergeCell ref="AP37:BP37"/>
+    <mergeCell ref="AP38:BP38"/>
+    <mergeCell ref="E44:Q44"/>
+    <mergeCell ref="R34:AO34"/>
+    <mergeCell ref="R35:AO35"/>
+    <mergeCell ref="R36:AO36"/>
+    <mergeCell ref="R37:AO37"/>
+    <mergeCell ref="E43:Q43"/>
+    <mergeCell ref="R43:AO43"/>
+    <mergeCell ref="R44:AO44"/>
     <mergeCell ref="E38:Q38"/>
     <mergeCell ref="E39:Q39"/>
     <mergeCell ref="E40:Q40"/>
     <mergeCell ref="E41:Q41"/>
     <mergeCell ref="E42:Q42"/>
-    <mergeCell ref="R38:AO38"/>
-    <mergeCell ref="R39:AO39"/>
-    <mergeCell ref="R40:AO40"/>
-    <mergeCell ref="R41:AO41"/>
-    <mergeCell ref="R42:AO42"/>
-    <mergeCell ref="R43:AO43"/>
-    <mergeCell ref="R44:AO44"/>
-    <mergeCell ref="AP34:BP34"/>
-    <mergeCell ref="AP35:BP35"/>
-    <mergeCell ref="AP36:BP36"/>
-    <mergeCell ref="AP37:BP37"/>
-    <mergeCell ref="AP38:BP38"/>
-    <mergeCell ref="AP39:BP39"/>
-    <mergeCell ref="AP40:BP40"/>
-    <mergeCell ref="AP41:BP41"/>
-    <mergeCell ref="E44:Q44"/>
-    <mergeCell ref="R34:AO34"/>
-    <mergeCell ref="R35:AO35"/>
-    <mergeCell ref="R36:AO36"/>
-    <mergeCell ref="R37:AO37"/>
-    <mergeCell ref="AP42:BP42"/>
-    <mergeCell ref="AP43:BP43"/>
-    <mergeCell ref="AP44:BP44"/>
-    <mergeCell ref="E43:Q43"/>
+    <mergeCell ref="E37:Q37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -6868,458 +6865,458 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AV72"/>
-  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="2:43" s="16" customFormat="1" ht="14.4" thickBot="1">
+    <row r="1" spans="2:43" s="16" customFormat="1" ht="15.75" thickBot="1">
       <c r="B1" s="15"/>
       <c r="D1" s="17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="2:43" ht="14.4" thickBot="1"/>
-    <row r="3" spans="2:43">
-      <c r="F3" s="43" t="s">
+    <row r="2" spans="2:43" ht="15" thickBot="1"/>
+    <row r="3" spans="2:43" ht="15">
+      <c r="F3" s="132" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31" t="s">
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31" t="s">
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="127"/>
+      <c r="V3" s="127"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
-      <c r="AD3" s="31"/>
-      <c r="AE3" s="31"/>
-      <c r="AF3" s="31"/>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="32"/>
+      <c r="Y3" s="127"/>
+      <c r="Z3" s="127"/>
+      <c r="AA3" s="127"/>
+      <c r="AB3" s="127"/>
+      <c r="AC3" s="127"/>
+      <c r="AD3" s="127"/>
+      <c r="AE3" s="127"/>
+      <c r="AF3" s="127"/>
+      <c r="AG3" s="127"/>
+      <c r="AH3" s="140"/>
     </row>
     <row r="4" spans="2:43">
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="33" t="s">
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33" t="s">
+      <c r="N4" s="130"/>
+      <c r="O4" s="130"/>
+      <c r="P4" s="130"/>
+      <c r="Q4" s="130"/>
+      <c r="R4" s="130"/>
+      <c r="S4" s="130"/>
+      <c r="T4" s="130"/>
+      <c r="U4" s="130"/>
+      <c r="V4" s="130"/>
+      <c r="W4" s="130"/>
+      <c r="X4" s="130" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="33"/>
-      <c r="AH4" s="34"/>
-      <c r="AI4" s="83" t="s">
+      <c r="Y4" s="130"/>
+      <c r="Z4" s="130"/>
+      <c r="AA4" s="130"/>
+      <c r="AB4" s="130"/>
+      <c r="AC4" s="130"/>
+      <c r="AD4" s="130"/>
+      <c r="AE4" s="130"/>
+      <c r="AF4" s="130"/>
+      <c r="AG4" s="130"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="AJ4" s="84"/>
-      <c r="AK4" s="84"/>
-      <c r="AL4" s="84"/>
-      <c r="AM4" s="84"/>
-      <c r="AN4" s="84"/>
-      <c r="AO4" s="84"/>
-      <c r="AP4" s="84"/>
-      <c r="AQ4" s="84"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="53"/>
+      <c r="AL4" s="53"/>
+      <c r="AM4" s="53"/>
+      <c r="AN4" s="53"/>
+      <c r="AO4" s="53"/>
+      <c r="AP4" s="53"/>
+      <c r="AQ4" s="53"/>
     </row>
     <row r="5" spans="2:43">
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="33" t="s">
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="128"/>
+      <c r="K5" s="128"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="130" t="s">
         <v>92</v>
       </c>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33" t="s">
+      <c r="N5" s="130"/>
+      <c r="O5" s="130"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="130"/>
+      <c r="R5" s="130"/>
+      <c r="S5" s="130"/>
+      <c r="T5" s="130"/>
+      <c r="U5" s="130"/>
+      <c r="V5" s="130"/>
+      <c r="W5" s="130"/>
+      <c r="X5" s="130" t="s">
         <v>93</v>
       </c>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="33"/>
-      <c r="AF5" s="33"/>
-      <c r="AG5" s="33"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="83"/>
-      <c r="AJ5" s="84"/>
-      <c r="AL5" s="84"/>
-      <c r="AM5" s="84"/>
-      <c r="AN5" s="84"/>
-      <c r="AO5" s="84"/>
-      <c r="AP5" s="84"/>
-      <c r="AQ5" s="84"/>
-    </row>
-    <row r="6" spans="2:43">
-      <c r="F6" s="37" t="s">
+      <c r="Y5" s="130"/>
+      <c r="Z5" s="130"/>
+      <c r="AA5" s="130"/>
+      <c r="AB5" s="130"/>
+      <c r="AC5" s="130"/>
+      <c r="AD5" s="130"/>
+      <c r="AE5" s="130"/>
+      <c r="AF5" s="130"/>
+      <c r="AG5" s="130"/>
+      <c r="AH5" s="138"/>
+      <c r="AI5" s="52"/>
+      <c r="AJ5" s="53"/>
+      <c r="AL5" s="53"/>
+      <c r="AM5" s="53"/>
+      <c r="AN5" s="53"/>
+      <c r="AO5" s="53"/>
+      <c r="AP5" s="53"/>
+      <c r="AQ5" s="53"/>
+    </row>
+    <row r="6" spans="2:43" ht="15">
+      <c r="F6" s="133" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="33" t="s">
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="128"/>
+      <c r="M6" s="130" t="s">
         <v>95</v>
       </c>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33" t="s">
+      <c r="N6" s="130"/>
+      <c r="O6" s="130"/>
+      <c r="P6" s="130"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="130"/>
+      <c r="S6" s="130"/>
+      <c r="T6" s="130"/>
+      <c r="U6" s="130"/>
+      <c r="V6" s="130"/>
+      <c r="W6" s="130"/>
+      <c r="X6" s="130" t="s">
         <v>96</v>
       </c>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="33"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33"/>
-      <c r="AH6" s="34"/>
-      <c r="AI6" s="83"/>
-      <c r="AJ6" s="84"/>
-      <c r="AK6" s="85" t="s">
+      <c r="Y6" s="130"/>
+      <c r="Z6" s="130"/>
+      <c r="AA6" s="130"/>
+      <c r="AB6" s="130"/>
+      <c r="AC6" s="130"/>
+      <c r="AD6" s="130"/>
+      <c r="AE6" s="130"/>
+      <c r="AF6" s="130"/>
+      <c r="AG6" s="130"/>
+      <c r="AH6" s="138"/>
+      <c r="AI6" s="52"/>
+      <c r="AJ6" s="53"/>
+      <c r="AK6" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="AL6" s="84"/>
-      <c r="AM6" s="84"/>
-      <c r="AN6" s="84"/>
-      <c r="AO6" s="84"/>
-      <c r="AP6" s="84"/>
-      <c r="AQ6" s="84"/>
+      <c r="AL6" s="53"/>
+      <c r="AM6" s="53"/>
+      <c r="AN6" s="53"/>
+      <c r="AO6" s="53"/>
+      <c r="AP6" s="53"/>
+      <c r="AQ6" s="53"/>
     </row>
     <row r="7" spans="2:43">
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="133" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="33" t="s">
+      <c r="G7" s="128"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="128"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="128"/>
+      <c r="L7" s="128"/>
+      <c r="M7" s="130" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33" t="s">
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+      <c r="Q7" s="130"/>
+      <c r="R7" s="130"/>
+      <c r="S7" s="130"/>
+      <c r="T7" s="130"/>
+      <c r="U7" s="130"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="130"/>
+      <c r="X7" s="130" t="s">
         <v>99</v>
       </c>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
-      <c r="AD7" s="33"/>
-      <c r="AE7" s="33"/>
-      <c r="AF7" s="33"/>
-      <c r="AG7" s="33"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="83"/>
-      <c r="AJ7" s="84"/>
-      <c r="AK7" s="84"/>
-      <c r="AL7" s="84"/>
-      <c r="AM7" s="84"/>
-      <c r="AN7" s="84"/>
-      <c r="AO7" s="84"/>
-      <c r="AP7" s="84"/>
-      <c r="AQ7" s="84"/>
+      <c r="Y7" s="130"/>
+      <c r="Z7" s="130"/>
+      <c r="AA7" s="130"/>
+      <c r="AB7" s="130"/>
+      <c r="AC7" s="130"/>
+      <c r="AD7" s="130"/>
+      <c r="AE7" s="130"/>
+      <c r="AF7" s="130"/>
+      <c r="AG7" s="130"/>
+      <c r="AH7" s="138"/>
+      <c r="AI7" s="52"/>
+      <c r="AJ7" s="53"/>
+      <c r="AK7" s="53"/>
+      <c r="AL7" s="53"/>
+      <c r="AM7" s="53"/>
+      <c r="AN7" s="53"/>
+      <c r="AO7" s="53"/>
+      <c r="AP7" s="53"/>
+      <c r="AQ7" s="53"/>
     </row>
     <row r="8" spans="2:43">
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="133" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="33" t="s">
+      <c r="G8" s="128"/>
+      <c r="H8" s="128"/>
+      <c r="I8" s="128"/>
+      <c r="J8" s="128"/>
+      <c r="K8" s="128"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="130" t="s">
         <v>101</v>
       </c>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33" t="s">
+      <c r="N8" s="130"/>
+      <c r="O8" s="130"/>
+      <c r="P8" s="130"/>
+      <c r="Q8" s="130"/>
+      <c r="R8" s="130"/>
+      <c r="S8" s="130"/>
+      <c r="T8" s="130"/>
+      <c r="U8" s="130"/>
+      <c r="V8" s="130"/>
+      <c r="W8" s="130"/>
+      <c r="X8" s="130" t="s">
         <v>102</v>
       </c>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="33"/>
-      <c r="AE8" s="33"/>
-      <c r="AF8" s="33"/>
-      <c r="AG8" s="33"/>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="83"/>
-      <c r="AJ8" s="84"/>
-      <c r="AK8" s="84"/>
-      <c r="AL8" s="84"/>
-      <c r="AM8" s="84"/>
-      <c r="AN8" s="84"/>
-      <c r="AO8" s="84"/>
-      <c r="AP8" s="84"/>
-      <c r="AQ8" s="84"/>
+      <c r="Y8" s="130"/>
+      <c r="Z8" s="130"/>
+      <c r="AA8" s="130"/>
+      <c r="AB8" s="130"/>
+      <c r="AC8" s="130"/>
+      <c r="AD8" s="130"/>
+      <c r="AE8" s="130"/>
+      <c r="AF8" s="130"/>
+      <c r="AG8" s="130"/>
+      <c r="AH8" s="138"/>
+      <c r="AI8" s="52"/>
+      <c r="AJ8" s="53"/>
+      <c r="AK8" s="53"/>
+      <c r="AL8" s="53"/>
+      <c r="AM8" s="53"/>
+      <c r="AN8" s="53"/>
+      <c r="AO8" s="53"/>
+      <c r="AP8" s="53"/>
+      <c r="AQ8" s="53"/>
     </row>
     <row r="9" spans="2:43">
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="33" t="s">
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="128"/>
+      <c r="J9" s="128"/>
+      <c r="K9" s="128"/>
+      <c r="L9" s="128"/>
+      <c r="M9" s="130" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33" t="s">
+      <c r="N9" s="130"/>
+      <c r="O9" s="130"/>
+      <c r="P9" s="130"/>
+      <c r="Q9" s="130"/>
+      <c r="R9" s="130"/>
+      <c r="S9" s="130"/>
+      <c r="T9" s="130"/>
+      <c r="U9" s="130"/>
+      <c r="V9" s="130"/>
+      <c r="W9" s="130"/>
+      <c r="X9" s="130" t="s">
         <v>104</v>
       </c>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
-      <c r="AD9" s="33"/>
-      <c r="AE9" s="33"/>
-      <c r="AF9" s="33"/>
-      <c r="AG9" s="33"/>
-      <c r="AH9" s="34"/>
-    </row>
-    <row r="10" spans="2:43" ht="24.6">
-      <c r="F10" s="37" t="s">
+      <c r="Y9" s="130"/>
+      <c r="Z9" s="130"/>
+      <c r="AA9" s="130"/>
+      <c r="AB9" s="130"/>
+      <c r="AC9" s="130"/>
+      <c r="AD9" s="130"/>
+      <c r="AE9" s="130"/>
+      <c r="AF9" s="130"/>
+      <c r="AG9" s="130"/>
+      <c r="AH9" s="138"/>
+    </row>
+    <row r="10" spans="2:43" ht="26.25">
+      <c r="F10" s="133" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="33" t="s">
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33" t="s">
+      <c r="N10" s="130"/>
+      <c r="O10" s="130"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="130"/>
+      <c r="R10" s="130"/>
+      <c r="S10" s="130"/>
+      <c r="T10" s="130"/>
+      <c r="U10" s="130"/>
+      <c r="V10" s="130"/>
+      <c r="W10" s="130"/>
+      <c r="X10" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="33"/>
-      <c r="AD10" s="33"/>
-      <c r="AE10" s="33"/>
-      <c r="AF10" s="33"/>
-      <c r="AG10" s="33"/>
-      <c r="AH10" s="34"/>
-      <c r="AK10" s="86" t="s">
+      <c r="Y10" s="130"/>
+      <c r="Z10" s="130"/>
+      <c r="AA10" s="130"/>
+      <c r="AB10" s="130"/>
+      <c r="AC10" s="130"/>
+      <c r="AD10" s="130"/>
+      <c r="AE10" s="130"/>
+      <c r="AF10" s="130"/>
+      <c r="AG10" s="130"/>
+      <c r="AH10" s="138"/>
+      <c r="AK10" s="55" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="11" spans="2:43">
-      <c r="F11" s="37" t="s">
+    <row r="11" spans="2:43" ht="15">
+      <c r="F11" s="133" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="33" t="s">
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33" t="s">
+      <c r="N11" s="130"/>
+      <c r="O11" s="130"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="130"/>
+      <c r="R11" s="130"/>
+      <c r="S11" s="130"/>
+      <c r="T11" s="130"/>
+      <c r="U11" s="130"/>
+      <c r="V11" s="130"/>
+      <c r="W11" s="130"/>
+      <c r="X11" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="33"/>
-      <c r="AE11" s="33"/>
-      <c r="AF11" s="33"/>
-      <c r="AG11" s="33"/>
-      <c r="AH11" s="34"/>
-      <c r="AL11" s="87" t="s">
+      <c r="Y11" s="130"/>
+      <c r="Z11" s="130"/>
+      <c r="AA11" s="130"/>
+      <c r="AB11" s="130"/>
+      <c r="AC11" s="130"/>
+      <c r="AD11" s="130"/>
+      <c r="AE11" s="130"/>
+      <c r="AF11" s="130"/>
+      <c r="AG11" s="130"/>
+      <c r="AH11" s="138"/>
+      <c r="AL11" s="56" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="2:43" ht="14.4" thickBot="1">
-      <c r="F12" s="35" t="s">
+    <row r="12" spans="2:43" ht="15" thickBot="1">
+      <c r="F12" s="134" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="29" t="s">
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="129"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="129"/>
+      <c r="M12" s="131" t="s">
         <v>111</v>
       </c>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29" t="s">
+      <c r="N12" s="131"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="131"/>
+      <c r="Q12" s="131"/>
+      <c r="R12" s="131"/>
+      <c r="S12" s="131"/>
+      <c r="T12" s="131"/>
+      <c r="U12" s="131"/>
+      <c r="V12" s="131"/>
+      <c r="W12" s="131"/>
+      <c r="X12" s="131" t="s">
         <v>112</v>
       </c>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29"/>
-      <c r="AA12" s="29"/>
-      <c r="AB12" s="29"/>
-      <c r="AC12" s="29"/>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="29"/>
-      <c r="AG12" s="29"/>
-      <c r="AH12" s="30"/>
-    </row>
-    <row r="13" spans="2:43" ht="14.4" thickBot="1"/>
-    <row r="14" spans="2:43" s="77" customFormat="1" ht="14.4" thickBot="1">
-      <c r="D14" s="78" t="s">
+      <c r="Y12" s="131"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="131"/>
+      <c r="AB12" s="131"/>
+      <c r="AC12" s="131"/>
+      <c r="AD12" s="131"/>
+      <c r="AE12" s="131"/>
+      <c r="AF12" s="131"/>
+      <c r="AG12" s="131"/>
+      <c r="AH12" s="139"/>
+    </row>
+    <row r="13" spans="2:43" ht="15" thickBot="1"/>
+    <row r="14" spans="2:43" s="46" customFormat="1" ht="15.75" thickBot="1">
+      <c r="D14" s="47" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="2:43" ht="14.4" thickBot="1"/>
-    <row r="16" spans="2:43" ht="14.4" thickBot="1">
-      <c r="C16" s="79" t="s">
+    <row r="15" spans="2:43" ht="15" thickBot="1"/>
+    <row r="16" spans="2:43" ht="15" thickBot="1">
+      <c r="C16" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="81"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="50"/>
     </row>
     <row r="17" spans="4:5">
       <c r="E17" t="s">
@@ -7375,7 +7372,7 @@
       </c>
     </row>
     <row r="29" spans="4:5">
-      <c r="E29" s="82" t="s">
+      <c r="E29" s="51" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7384,33 +7381,33 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="4:5" ht="14.4" thickBot="1"/>
-    <row r="32" spans="4:5" s="77" customFormat="1" ht="14.4" thickBot="1">
-      <c r="D32" s="78" t="s">
+    <row r="31" spans="4:5" ht="15" thickBot="1"/>
+    <row r="32" spans="4:5" s="46" customFormat="1" ht="15.75" thickBot="1">
+      <c r="D32" s="47" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="33" spans="3:35" ht="14.4" thickBot="1"/>
-    <row r="34" spans="3:35" ht="14.4" thickBot="1">
-      <c r="C34" s="79" t="s">
+    <row r="33" spans="3:35" ht="15" thickBot="1"/>
+    <row r="34" spans="3:35" ht="15" thickBot="1">
+      <c r="C34" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="D34" s="80"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="80"/>
-      <c r="G34" s="80"/>
-      <c r="H34" s="80"/>
-      <c r="I34" s="80"/>
-      <c r="J34" s="80"/>
-      <c r="K34" s="81"/>
-      <c r="AD34" s="79" t="s">
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="49"/>
+      <c r="J34" s="49"/>
+      <c r="K34" s="50"/>
+      <c r="AD34" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="AE34" s="80"/>
-      <c r="AF34" s="80"/>
-      <c r="AG34" s="80"/>
-      <c r="AH34" s="80"/>
-      <c r="AI34" s="81"/>
+      <c r="AE34" s="49"/>
+      <c r="AF34" s="49"/>
+      <c r="AG34" s="49"/>
+      <c r="AH34" s="49"/>
+      <c r="AI34" s="50"/>
     </row>
     <row r="35" spans="3:35">
       <c r="E35" t="s">
@@ -7542,7 +7539,7 @@
       </c>
     </row>
     <row r="54" spans="5:48">
-      <c r="E54" s="82" t="s">
+      <c r="E54" s="51" t="s">
         <v>168</v>
       </c>
       <c r="AF54" t="s">
@@ -7570,24 +7567,24 @@
         <v>174</v>
       </c>
     </row>
-    <row r="58" spans="5:48" ht="14.4" thickBot="1">
+    <row r="58" spans="5:48" ht="15" thickBot="1">
       <c r="E58" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="59" spans="5:48" ht="14.4" thickBot="1">
-      <c r="AF59" s="82" t="s">
+    <row r="59" spans="5:48" ht="15" thickBot="1">
+      <c r="AF59" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="AP59" s="120" t="s">
+      <c r="AP59" s="83" t="s">
         <v>272</v>
       </c>
-      <c r="AQ59" s="108"/>
-      <c r="AR59" s="108"/>
-      <c r="AS59" s="108"/>
-      <c r="AT59" s="108"/>
-      <c r="AU59" s="108"/>
-      <c r="AV59" s="109"/>
+      <c r="AQ59" s="71"/>
+      <c r="AR59" s="71"/>
+      <c r="AS59" s="71"/>
+      <c r="AT59" s="71"/>
+      <c r="AU59" s="71"/>
+      <c r="AV59" s="72"/>
     </row>
     <row r="60" spans="5:48">
       <c r="E60" t="s">
@@ -7651,9 +7648,9 @@
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="4:32" ht="14.4" thickBot="1"/>
-    <row r="72" spans="4:32" s="77" customFormat="1" ht="14.4" thickBot="1">
-      <c r="D72" s="78" t="s">
+    <row r="71" spans="4:32" ht="15" thickBot="1"/>
+    <row r="72" spans="4:32" s="46" customFormat="1" ht="15.75" thickBot="1">
+      <c r="D72" s="47" t="s">
         <v>271</v>
       </c>
     </row>
@@ -7673,22 +7670,22 @@
     <mergeCell ref="M9:W9"/>
     <mergeCell ref="M10:W10"/>
     <mergeCell ref="M11:W11"/>
+    <mergeCell ref="M3:W3"/>
+    <mergeCell ref="M4:W4"/>
+    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="F12:L12"/>
     <mergeCell ref="F6:L6"/>
     <mergeCell ref="F7:L7"/>
     <mergeCell ref="F8:L8"/>
     <mergeCell ref="F9:L9"/>
     <mergeCell ref="F10:L10"/>
-    <mergeCell ref="F11:L11"/>
-    <mergeCell ref="F5:L5"/>
-    <mergeCell ref="F3:L3"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="F12:L12"/>
-    <mergeCell ref="M3:W3"/>
-    <mergeCell ref="M4:W4"/>
     <mergeCell ref="M5:W5"/>
     <mergeCell ref="M6:W6"/>
     <mergeCell ref="M7:W7"/>
     <mergeCell ref="M8:W8"/>
+    <mergeCell ref="F11:L11"/>
+    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7698,813 +7695,813 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C5C6D57-9A86-4D22-90DF-F0D5383CEF40}">
   <dimension ref="A1:BK47"/>
-  <sheetFormatPr defaultColWidth="2.796875" defaultRowHeight="13.8" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="13.9" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:63" ht="13.8" customHeight="1" thickBot="1">
-      <c r="C1" s="110"/>
-    </row>
-    <row r="2" spans="1:63" s="108" customFormat="1" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A2" s="107"/>
-      <c r="B2" s="118" t="s">
+    <row r="1" spans="1:63" ht="13.9" customHeight="1" thickBot="1">
+      <c r="C1" s="73"/>
+    </row>
+    <row r="2" spans="1:63" s="71" customFormat="1" ht="13.9" customHeight="1" thickBot="1">
+      <c r="A2" s="70"/>
+      <c r="B2" s="81" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="117"/>
-    </row>
-    <row r="3" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C3" s="111"/>
-    </row>
-    <row r="4" spans="1:63" ht="22.8">
-      <c r="C4" s="110" t="s">
+      <c r="C2" s="80"/>
+    </row>
+    <row r="3" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C3" s="74"/>
+    </row>
+    <row r="4" spans="1:63" ht="23.25">
+      <c r="C4" s="73" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:63" ht="13.8" customHeight="1">
-      <c r="E5" s="113" t="s">
+    <row r="5" spans="1:63" ht="13.9" customHeight="1">
+      <c r="E5" s="76" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:63" ht="13.8" customHeight="1">
-      <c r="E6" s="119" t="s">
+    <row r="6" spans="1:63" ht="13.9" customHeight="1">
+      <c r="E6" s="82" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:63" ht="13.8" customHeight="1">
-      <c r="E7" s="119" t="s">
+    <row r="7" spans="1:63" ht="13.9" customHeight="1">
+      <c r="E7" s="82" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:63" ht="13.8" customHeight="1">
-      <c r="E8" s="119" t="s">
+    <row r="8" spans="1:63" ht="13.9" customHeight="1">
+      <c r="E8" s="82" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="9" spans="1:63" ht="13.8" customHeight="1">
-      <c r="E9" s="119" t="s">
+    <row r="9" spans="1:63" ht="13.9" customHeight="1">
+      <c r="E9" s="82" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C11" s="112"/>
-      <c r="D11" s="121" t="s">
+    <row r="11" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C11" s="75"/>
+      <c r="D11" s="84" t="s">
         <v>273</v>
       </c>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="122"/>
-      <c r="P11" s="122"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="122"/>
-      <c r="T11" s="122"/>
-      <c r="U11" s="122"/>
-      <c r="V11" s="122"/>
-      <c r="W11" s="122"/>
-      <c r="X11" s="122"/>
-      <c r="Y11" s="122"/>
-      <c r="Z11" s="122"/>
-      <c r="AA11" s="122"/>
-      <c r="AB11" s="122"/>
-      <c r="AC11" s="122"/>
-      <c r="AD11" s="122"/>
-      <c r="AE11" s="122"/>
-      <c r="AF11" s="123"/>
-    </row>
-    <row r="12" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C12" s="112"/>
-      <c r="D12" s="124" t="s">
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
+      <c r="S11" s="85"/>
+      <c r="T11" s="85"/>
+      <c r="U11" s="85"/>
+      <c r="V11" s="85"/>
+      <c r="W11" s="85"/>
+      <c r="X11" s="85"/>
+      <c r="Y11" s="85"/>
+      <c r="Z11" s="85"/>
+      <c r="AA11" s="85"/>
+      <c r="AB11" s="85"/>
+      <c r="AC11" s="85"/>
+      <c r="AD11" s="85"/>
+      <c r="AE11" s="85"/>
+      <c r="AF11" s="86"/>
+    </row>
+    <row r="12" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C12" s="75"/>
+      <c r="D12" s="87" t="s">
         <v>274</v>
       </c>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="125"/>
-      <c r="L12" s="125"/>
-      <c r="M12" s="125"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="125"/>
-      <c r="P12" s="125"/>
-      <c r="Q12" s="125"/>
-      <c r="R12" s="125"/>
-      <c r="S12" s="125"/>
-      <c r="T12" s="125"/>
-      <c r="U12" s="125"/>
-      <c r="V12" s="125"/>
-      <c r="W12" s="125"/>
-      <c r="X12" s="125"/>
-      <c r="Y12" s="125"/>
-      <c r="Z12" s="125"/>
-      <c r="AA12" s="125"/>
-      <c r="AB12" s="125"/>
-      <c r="AC12" s="125"/>
-      <c r="AD12" s="125"/>
-      <c r="AE12" s="125"/>
-      <c r="AF12" s="126"/>
-    </row>
-    <row r="13" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C13" s="112"/>
-      <c r="D13" s="124" t="s">
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="88"/>
+      <c r="L12" s="88"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="88"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88"/>
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="88"/>
+      <c r="AF12" s="89"/>
+    </row>
+    <row r="13" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C13" s="75"/>
+      <c r="D13" s="87" t="s">
         <v>275</v>
       </c>
-      <c r="E13" s="125"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="125"/>
-      <c r="K13" s="125"/>
-      <c r="L13" s="125"/>
-      <c r="M13" s="125"/>
-      <c r="N13" s="125"/>
-      <c r="O13" s="125"/>
-      <c r="P13" s="125"/>
-      <c r="Q13" s="125"/>
-      <c r="R13" s="125"/>
-      <c r="S13" s="125"/>
-      <c r="T13" s="125"/>
-      <c r="U13" s="125"/>
-      <c r="V13" s="125"/>
-      <c r="W13" s="125"/>
-      <c r="X13" s="125"/>
-      <c r="Y13" s="125"/>
-      <c r="Z13" s="125"/>
-      <c r="AA13" s="125"/>
-      <c r="AB13" s="125"/>
-      <c r="AC13" s="125"/>
-      <c r="AD13" s="125"/>
-      <c r="AE13" s="125"/>
-      <c r="AF13" s="126"/>
-    </row>
-    <row r="14" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C14" s="112"/>
-      <c r="D14" s="127" t="s">
+      <c r="E13" s="88"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="88"/>
+      <c r="H13" s="88"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88"/>
+      <c r="K13" s="88"/>
+      <c r="L13" s="88"/>
+      <c r="M13" s="88"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="88"/>
+      <c r="P13" s="88"/>
+      <c r="Q13" s="88"/>
+      <c r="R13" s="88"/>
+      <c r="S13" s="88"/>
+      <c r="T13" s="88"/>
+      <c r="U13" s="88"/>
+      <c r="V13" s="88"/>
+      <c r="W13" s="88"/>
+      <c r="X13" s="88"/>
+      <c r="Y13" s="88"/>
+      <c r="Z13" s="88"/>
+      <c r="AA13" s="88"/>
+      <c r="AB13" s="88"/>
+      <c r="AC13" s="88"/>
+      <c r="AD13" s="88"/>
+      <c r="AE13" s="88"/>
+      <c r="AF13" s="89"/>
+    </row>
+    <row r="14" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C14" s="75"/>
+      <c r="D14" s="90" t="s">
         <v>276</v>
       </c>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="125"/>
-      <c r="K14" s="125"/>
-      <c r="L14" s="125"/>
-      <c r="M14" s="125"/>
-      <c r="N14" s="125"/>
-      <c r="O14" s="125"/>
-      <c r="P14" s="125"/>
-      <c r="Q14" s="125"/>
-      <c r="R14" s="125"/>
-      <c r="S14" s="125"/>
-      <c r="T14" s="125"/>
-      <c r="U14" s="125"/>
-      <c r="V14" s="125"/>
-      <c r="W14" s="125"/>
-      <c r="X14" s="125"/>
-      <c r="Y14" s="125"/>
-      <c r="Z14" s="125"/>
-      <c r="AA14" s="125"/>
-      <c r="AB14" s="125"/>
-      <c r="AC14" s="125"/>
-      <c r="AD14" s="125"/>
-      <c r="AE14" s="125"/>
-      <c r="AF14" s="126"/>
-    </row>
-    <row r="15" spans="1:63" ht="13.8" customHeight="1" thickBot="1">
-      <c r="C15" s="110"/>
-      <c r="D15" s="127" t="s">
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="88"/>
+      <c r="L14" s="88"/>
+      <c r="M14" s="88"/>
+      <c r="N14" s="88"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="88"/>
+      <c r="R14" s="88"/>
+      <c r="S14" s="88"/>
+      <c r="T14" s="88"/>
+      <c r="U14" s="88"/>
+      <c r="V14" s="88"/>
+      <c r="W14" s="88"/>
+      <c r="X14" s="88"/>
+      <c r="Y14" s="88"/>
+      <c r="Z14" s="88"/>
+      <c r="AA14" s="88"/>
+      <c r="AB14" s="88"/>
+      <c r="AC14" s="88"/>
+      <c r="AD14" s="88"/>
+      <c r="AE14" s="88"/>
+      <c r="AF14" s="89"/>
+    </row>
+    <row r="15" spans="1:63" ht="13.9" customHeight="1" thickBot="1">
+      <c r="C15" s="73"/>
+      <c r="D15" s="90" t="s">
         <v>277</v>
       </c>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="125"/>
-      <c r="L15" s="125"/>
-      <c r="M15" s="125"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="125"/>
-      <c r="P15" s="125"/>
-      <c r="Q15" s="125"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="125"/>
-      <c r="T15" s="125"/>
-      <c r="U15" s="125"/>
-      <c r="V15" s="125"/>
-      <c r="W15" s="125"/>
-      <c r="X15" s="125"/>
-      <c r="Y15" s="125"/>
-      <c r="Z15" s="125"/>
-      <c r="AA15" s="125"/>
-      <c r="AB15" s="125"/>
-      <c r="AC15" s="125"/>
-      <c r="AD15" s="125"/>
-      <c r="AE15" s="125"/>
-      <c r="AF15" s="126"/>
-    </row>
-    <row r="16" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C16" s="111"/>
-      <c r="D16" s="128" t="s">
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="88"/>
+      <c r="K15" s="88"/>
+      <c r="L15" s="88"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
+      <c r="R15" s="88"/>
+      <c r="S15" s="88"/>
+      <c r="T15" s="88"/>
+      <c r="U15" s="88"/>
+      <c r="V15" s="88"/>
+      <c r="W15" s="88"/>
+      <c r="X15" s="88"/>
+      <c r="Y15" s="88"/>
+      <c r="Z15" s="88"/>
+      <c r="AA15" s="88"/>
+      <c r="AB15" s="88"/>
+      <c r="AC15" s="88"/>
+      <c r="AD15" s="88"/>
+      <c r="AE15" s="88"/>
+      <c r="AF15" s="89"/>
+    </row>
+    <row r="16" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C16" s="74"/>
+      <c r="D16" s="91" t="s">
         <v>278</v>
       </c>
-      <c r="E16" s="129"/>
-      <c r="F16" s="129"/>
-      <c r="G16" s="129"/>
-      <c r="H16" s="129"/>
-      <c r="I16" s="129"/>
-      <c r="J16" s="129"/>
-      <c r="K16" s="129"/>
-      <c r="L16" s="129"/>
-      <c r="M16" s="129"/>
-      <c r="N16" s="129"/>
-      <c r="O16" s="129"/>
-      <c r="P16" s="129"/>
-      <c r="Q16" s="129"/>
-      <c r="R16" s="129"/>
-      <c r="S16" s="129"/>
-      <c r="T16" s="129"/>
-      <c r="U16" s="129"/>
-      <c r="V16" s="129"/>
-      <c r="W16" s="129"/>
-      <c r="X16" s="129"/>
-      <c r="Y16" s="129"/>
-      <c r="Z16" s="129"/>
-      <c r="AA16" s="129"/>
-      <c r="AB16" s="129"/>
-      <c r="AC16" s="129"/>
-      <c r="AD16" s="129"/>
-      <c r="AE16" s="129"/>
-      <c r="AF16" s="130"/>
-      <c r="AI16" s="137" t="s">
+      <c r="E16" s="92"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="92"/>
+      <c r="O16" s="92"/>
+      <c r="P16" s="92"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="92"/>
+      <c r="S16" s="92"/>
+      <c r="T16" s="92"/>
+      <c r="U16" s="92"/>
+      <c r="V16" s="92"/>
+      <c r="W16" s="92"/>
+      <c r="X16" s="92"/>
+      <c r="Y16" s="92"/>
+      <c r="Z16" s="92"/>
+      <c r="AA16" s="92"/>
+      <c r="AB16" s="92"/>
+      <c r="AC16" s="92"/>
+      <c r="AD16" s="92"/>
+      <c r="AE16" s="92"/>
+      <c r="AF16" s="93"/>
+      <c r="AI16" s="100" t="s">
         <v>298</v>
       </c>
-      <c r="AJ16" s="138"/>
-      <c r="AK16" s="138"/>
-      <c r="AL16" s="138"/>
-      <c r="AM16" s="138"/>
-      <c r="AN16" s="138"/>
-      <c r="AO16" s="138"/>
-      <c r="AP16" s="138"/>
-      <c r="AQ16" s="138"/>
-      <c r="AR16" s="138"/>
-      <c r="AS16" s="138"/>
-      <c r="AT16" s="138"/>
-      <c r="AU16" s="138"/>
-      <c r="AV16" s="138"/>
-      <c r="AW16" s="138"/>
-      <c r="AX16" s="138"/>
-      <c r="AY16" s="138"/>
-      <c r="AZ16" s="138"/>
-      <c r="BA16" s="138"/>
-      <c r="BB16" s="138"/>
-      <c r="BC16" s="138"/>
-      <c r="BD16" s="138"/>
-      <c r="BE16" s="138"/>
-      <c r="BF16" s="138"/>
-      <c r="BG16" s="138"/>
-      <c r="BH16" s="138"/>
-      <c r="BI16" s="138"/>
-      <c r="BJ16" s="138"/>
-      <c r="BK16" s="139"/>
-    </row>
-    <row r="17" spans="1:63" ht="13.8" customHeight="1" thickBot="1">
-      <c r="C17" s="112"/>
-      <c r="AI17" s="140"/>
-      <c r="AJ17" s="141" t="s">
+      <c r="AJ16" s="101"/>
+      <c r="AK16" s="101"/>
+      <c r="AL16" s="101"/>
+      <c r="AM16" s="101"/>
+      <c r="AN16" s="101"/>
+      <c r="AO16" s="101"/>
+      <c r="AP16" s="101"/>
+      <c r="AQ16" s="101"/>
+      <c r="AR16" s="101"/>
+      <c r="AS16" s="101"/>
+      <c r="AT16" s="101"/>
+      <c r="AU16" s="101"/>
+      <c r="AV16" s="101"/>
+      <c r="AW16" s="101"/>
+      <c r="AX16" s="101"/>
+      <c r="AY16" s="101"/>
+      <c r="AZ16" s="101"/>
+      <c r="BA16" s="101"/>
+      <c r="BB16" s="101"/>
+      <c r="BC16" s="101"/>
+      <c r="BD16" s="101"/>
+      <c r="BE16" s="101"/>
+      <c r="BF16" s="101"/>
+      <c r="BG16" s="101"/>
+      <c r="BH16" s="101"/>
+      <c r="BI16" s="101"/>
+      <c r="BJ16" s="101"/>
+      <c r="BK16" s="102"/>
+    </row>
+    <row r="17" spans="1:63" ht="13.9" customHeight="1" thickBot="1">
+      <c r="C17" s="75"/>
+      <c r="AI17" s="103"/>
+      <c r="AJ17" s="104" t="s">
         <v>299</v>
       </c>
-      <c r="AK17" s="141"/>
-      <c r="AL17" s="141"/>
-      <c r="AM17" s="141"/>
-      <c r="AN17" s="141"/>
-      <c r="AO17" s="141"/>
-      <c r="AP17" s="141"/>
-      <c r="AQ17" s="141"/>
-      <c r="AR17" s="141"/>
-      <c r="AS17" s="141"/>
-      <c r="AT17" s="141"/>
-      <c r="AU17" s="141"/>
-      <c r="AV17" s="141"/>
-      <c r="AW17" s="141"/>
-      <c r="AX17" s="141"/>
-      <c r="AY17" s="141"/>
-      <c r="AZ17" s="141"/>
-      <c r="BA17" s="141"/>
-      <c r="BB17" s="141"/>
-      <c r="BC17" s="141"/>
-      <c r="BD17" s="141"/>
-      <c r="BE17" s="141"/>
-      <c r="BF17" s="141"/>
-      <c r="BG17" s="141"/>
-      <c r="BH17" s="141"/>
-      <c r="BI17" s="141"/>
-      <c r="BJ17" s="141"/>
-      <c r="BK17" s="142"/>
-    </row>
-    <row r="18" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C18" s="112"/>
-      <c r="D18" s="121" t="s">
+      <c r="AK17" s="104"/>
+      <c r="AL17" s="104"/>
+      <c r="AM17" s="104"/>
+      <c r="AN17" s="104"/>
+      <c r="AO17" s="104"/>
+      <c r="AP17" s="104"/>
+      <c r="AQ17" s="104"/>
+      <c r="AR17" s="104"/>
+      <c r="AS17" s="104"/>
+      <c r="AT17" s="104"/>
+      <c r="AU17" s="104"/>
+      <c r="AV17" s="104"/>
+      <c r="AW17" s="104"/>
+      <c r="AX17" s="104"/>
+      <c r="AY17" s="104"/>
+      <c r="AZ17" s="104"/>
+      <c r="BA17" s="104"/>
+      <c r="BB17" s="104"/>
+      <c r="BC17" s="104"/>
+      <c r="BD17" s="104"/>
+      <c r="BE17" s="104"/>
+      <c r="BF17" s="104"/>
+      <c r="BG17" s="104"/>
+      <c r="BH17" s="104"/>
+      <c r="BI17" s="104"/>
+      <c r="BJ17" s="104"/>
+      <c r="BK17" s="105"/>
+    </row>
+    <row r="18" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C18" s="75"/>
+      <c r="D18" s="84" t="s">
         <v>279</v>
       </c>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="122"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="122"/>
-      <c r="S18" s="122"/>
-      <c r="T18" s="122"/>
-      <c r="U18" s="122"/>
-      <c r="V18" s="122"/>
-      <c r="W18" s="122"/>
-      <c r="X18" s="122"/>
-      <c r="Y18" s="122"/>
-      <c r="Z18" s="122"/>
-      <c r="AA18" s="122"/>
-      <c r="AB18" s="122"/>
-      <c r="AC18" s="122"/>
-      <c r="AD18" s="122"/>
-      <c r="AE18" s="122"/>
-      <c r="AF18" s="123"/>
-    </row>
-    <row r="19" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C19" s="112"/>
-      <c r="D19" s="124" t="s">
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="85"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="85"/>
+      <c r="X18" s="85"/>
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="85"/>
+      <c r="AE18" s="85"/>
+      <c r="AF18" s="86"/>
+    </row>
+    <row r="19" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C19" s="75"/>
+      <c r="D19" s="87" t="s">
         <v>280</v>
       </c>
-      <c r="E19" s="125"/>
-      <c r="F19" s="125"/>
-      <c r="G19" s="125"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="125"/>
-      <c r="K19" s="125"/>
-      <c r="L19" s="125"/>
-      <c r="M19" s="125"/>
-      <c r="N19" s="125"/>
-      <c r="O19" s="125"/>
-      <c r="P19" s="125"/>
-      <c r="Q19" s="125"/>
-      <c r="R19" s="125"/>
-      <c r="S19" s="125"/>
-      <c r="T19" s="125"/>
-      <c r="U19" s="125"/>
-      <c r="V19" s="125"/>
-      <c r="W19" s="125"/>
-      <c r="X19" s="125"/>
-      <c r="Y19" s="125"/>
-      <c r="Z19" s="125"/>
-      <c r="AA19" s="125"/>
-      <c r="AB19" s="125"/>
-      <c r="AC19" s="125"/>
-      <c r="AD19" s="125"/>
-      <c r="AE19" s="125"/>
-      <c r="AF19" s="126"/>
-    </row>
-    <row r="20" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C20" s="113"/>
-      <c r="D20" s="124" t="s">
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="88"/>
+      <c r="K19" s="88"/>
+      <c r="L19" s="88"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="88"/>
+      <c r="Q19" s="88"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="88"/>
+      <c r="V19" s="88"/>
+      <c r="W19" s="88"/>
+      <c r="X19" s="88"/>
+      <c r="Y19" s="88"/>
+      <c r="Z19" s="88"/>
+      <c r="AA19" s="88"/>
+      <c r="AB19" s="88"/>
+      <c r="AC19" s="88"/>
+      <c r="AD19" s="88"/>
+      <c r="AE19" s="88"/>
+      <c r="AF19" s="89"/>
+    </row>
+    <row r="20" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C20" s="76"/>
+      <c r="D20" s="87" t="s">
         <v>281</v>
       </c>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="125"/>
-      <c r="H20" s="125"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="125"/>
-      <c r="K20" s="125"/>
-      <c r="L20" s="125"/>
-      <c r="M20" s="125"/>
-      <c r="N20" s="125"/>
-      <c r="O20" s="125"/>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="125"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="125"/>
-      <c r="T20" s="125"/>
-      <c r="U20" s="125"/>
-      <c r="V20" s="125"/>
-      <c r="W20" s="125"/>
-      <c r="X20" s="125"/>
-      <c r="Y20" s="125"/>
-      <c r="Z20" s="125"/>
-      <c r="AA20" s="125"/>
-      <c r="AB20" s="125"/>
-      <c r="AC20" s="125"/>
-      <c r="AD20" s="125"/>
-      <c r="AE20" s="125"/>
-      <c r="AF20" s="126"/>
-    </row>
-    <row r="21" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C21" s="112"/>
-      <c r="D21" s="127" t="s">
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="88"/>
+      <c r="L20" s="88"/>
+      <c r="M20" s="88"/>
+      <c r="N20" s="88"/>
+      <c r="O20" s="88"/>
+      <c r="P20" s="88"/>
+      <c r="Q20" s="88"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="88"/>
+      <c r="T20" s="88"/>
+      <c r="U20" s="88"/>
+      <c r="V20" s="88"/>
+      <c r="W20" s="88"/>
+      <c r="X20" s="88"/>
+      <c r="Y20" s="88"/>
+      <c r="Z20" s="88"/>
+      <c r="AA20" s="88"/>
+      <c r="AB20" s="88"/>
+      <c r="AC20" s="88"/>
+      <c r="AD20" s="88"/>
+      <c r="AE20" s="88"/>
+      <c r="AF20" s="89"/>
+    </row>
+    <row r="21" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C21" s="75"/>
+      <c r="D21" s="90" t="s">
         <v>282</v>
       </c>
-      <c r="E21" s="125"/>
-      <c r="F21" s="125"/>
-      <c r="G21" s="125"/>
-      <c r="H21" s="125"/>
-      <c r="I21" s="125"/>
-      <c r="J21" s="125"/>
-      <c r="K21" s="125"/>
-      <c r="L21" s="125"/>
-      <c r="M21" s="125"/>
-      <c r="N21" s="125"/>
-      <c r="O21" s="125"/>
-      <c r="P21" s="125"/>
-      <c r="Q21" s="125"/>
-      <c r="R21" s="125"/>
-      <c r="S21" s="125"/>
-      <c r="T21" s="125"/>
-      <c r="U21" s="125"/>
-      <c r="V21" s="125"/>
-      <c r="W21" s="125"/>
-      <c r="X21" s="125"/>
-      <c r="Y21" s="125"/>
-      <c r="Z21" s="125"/>
-      <c r="AA21" s="125"/>
-      <c r="AB21" s="125"/>
-      <c r="AC21" s="125"/>
-      <c r="AD21" s="125"/>
-      <c r="AE21" s="125"/>
-      <c r="AF21" s="126"/>
-    </row>
-    <row r="22" spans="1:63" ht="13.8" customHeight="1">
-      <c r="D22" s="127" t="s">
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="88"/>
+      <c r="J21" s="88"/>
+      <c r="K21" s="88"/>
+      <c r="L21" s="88"/>
+      <c r="M21" s="88"/>
+      <c r="N21" s="88"/>
+      <c r="O21" s="88"/>
+      <c r="P21" s="88"/>
+      <c r="Q21" s="88"/>
+      <c r="R21" s="88"/>
+      <c r="S21" s="88"/>
+      <c r="T21" s="88"/>
+      <c r="U21" s="88"/>
+      <c r="V21" s="88"/>
+      <c r="W21" s="88"/>
+      <c r="X21" s="88"/>
+      <c r="Y21" s="88"/>
+      <c r="Z21" s="88"/>
+      <c r="AA21" s="88"/>
+      <c r="AB21" s="88"/>
+      <c r="AC21" s="88"/>
+      <c r="AD21" s="88"/>
+      <c r="AE21" s="88"/>
+      <c r="AF21" s="89"/>
+    </row>
+    <row r="22" spans="1:63" ht="13.9" customHeight="1">
+      <c r="D22" s="90" t="s">
         <v>283</v>
       </c>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="125"/>
-      <c r="N22" s="125"/>
-      <c r="O22" s="125"/>
-      <c r="P22" s="125"/>
-      <c r="Q22" s="125"/>
-      <c r="R22" s="125"/>
-      <c r="S22" s="125"/>
-      <c r="T22" s="125"/>
-      <c r="U22" s="125"/>
-      <c r="V22" s="125"/>
-      <c r="W22" s="125"/>
-      <c r="X22" s="125"/>
-      <c r="Y22" s="125"/>
-      <c r="Z22" s="125"/>
-      <c r="AA22" s="125"/>
-      <c r="AB22" s="125"/>
-      <c r="AC22" s="125"/>
-      <c r="AD22" s="125"/>
-      <c r="AE22" s="125"/>
-      <c r="AF22" s="126"/>
-    </row>
-    <row r="23" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C23" s="111"/>
-      <c r="D23" s="128" t="s">
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="88"/>
+      <c r="L22" s="88"/>
+      <c r="M22" s="88"/>
+      <c r="N22" s="88"/>
+      <c r="O22" s="88"/>
+      <c r="P22" s="88"/>
+      <c r="Q22" s="88"/>
+      <c r="R22" s="88"/>
+      <c r="S22" s="88"/>
+      <c r="T22" s="88"/>
+      <c r="U22" s="88"/>
+      <c r="V22" s="88"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="88"/>
+      <c r="AA22" s="88"/>
+      <c r="AB22" s="88"/>
+      <c r="AC22" s="88"/>
+      <c r="AD22" s="88"/>
+      <c r="AE22" s="88"/>
+      <c r="AF22" s="89"/>
+    </row>
+    <row r="23" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C23" s="74"/>
+      <c r="D23" s="91" t="s">
         <v>284</v>
       </c>
-      <c r="E23" s="129"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="129"/>
-      <c r="K23" s="129"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="129"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="129"/>
-      <c r="Q23" s="129"/>
-      <c r="R23" s="129"/>
-      <c r="S23" s="129"/>
-      <c r="T23" s="129"/>
-      <c r="U23" s="129"/>
-      <c r="V23" s="129"/>
-      <c r="W23" s="129"/>
-      <c r="X23" s="129"/>
-      <c r="Y23" s="129"/>
-      <c r="Z23" s="129"/>
-      <c r="AA23" s="129"/>
-      <c r="AB23" s="129"/>
-      <c r="AC23" s="129"/>
-      <c r="AD23" s="129"/>
-      <c r="AE23" s="129"/>
-      <c r="AF23" s="130"/>
-    </row>
-    <row r="24" spans="1:63" ht="13.8" customHeight="1" thickBot="1">
-      <c r="C24" s="111"/>
-    </row>
-    <row r="25" spans="1:63" s="108" customFormat="1" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A25" s="107"/>
-      <c r="B25" s="118" t="s">
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="92"/>
+      <c r="O23" s="92"/>
+      <c r="P23" s="92"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="92"/>
+      <c r="S23" s="92"/>
+      <c r="T23" s="92"/>
+      <c r="U23" s="92"/>
+      <c r="V23" s="92"/>
+      <c r="W23" s="92"/>
+      <c r="X23" s="92"/>
+      <c r="Y23" s="92"/>
+      <c r="Z23" s="92"/>
+      <c r="AA23" s="92"/>
+      <c r="AB23" s="92"/>
+      <c r="AC23" s="92"/>
+      <c r="AD23" s="92"/>
+      <c r="AE23" s="92"/>
+      <c r="AF23" s="93"/>
+    </row>
+    <row r="24" spans="1:63" ht="13.9" customHeight="1" thickBot="1">
+      <c r="C24" s="74"/>
+    </row>
+    <row r="25" spans="1:63" s="71" customFormat="1" ht="13.9" customHeight="1" thickBot="1">
+      <c r="A25" s="70"/>
+      <c r="B25" s="81" t="s">
         <v>285</v>
       </c>
-      <c r="C25" s="117"/>
-    </row>
-    <row r="26" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C26" s="114"/>
-    </row>
-    <row r="27" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C27" s="114"/>
+      <c r="C25" s="80"/>
+    </row>
+    <row r="26" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C26" s="77"/>
+    </row>
+    <row r="27" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C27" s="77"/>
       <c r="D27" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="28" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C28" s="111"/>
-    </row>
-    <row r="29" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C29" s="131" t="s">
+    <row r="28" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C28" s="74"/>
+    </row>
+    <row r="29" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C29" s="94" t="s">
         <v>287</v>
       </c>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="122"/>
-      <c r="G29" s="122"/>
-      <c r="H29" s="122"/>
-      <c r="I29" s="122"/>
-      <c r="J29" s="122"/>
-      <c r="K29" s="122"/>
-      <c r="L29" s="122"/>
-      <c r="M29" s="122"/>
-      <c r="N29" s="122"/>
-      <c r="O29" s="122"/>
-      <c r="P29" s="122"/>
-      <c r="Q29" s="123"/>
-      <c r="U29" s="136" t="s">
+      <c r="D29" s="85"/>
+      <c r="E29" s="85"/>
+      <c r="F29" s="85"/>
+      <c r="G29" s="85"/>
+      <c r="H29" s="85"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
+      <c r="M29" s="85"/>
+      <c r="N29" s="85"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="86"/>
+      <c r="U29" s="99" t="s">
         <v>295</v>
       </c>
-      <c r="V29" s="122"/>
-      <c r="W29" s="122"/>
-      <c r="X29" s="122"/>
-      <c r="Y29" s="122"/>
-      <c r="Z29" s="122"/>
-      <c r="AA29" s="122"/>
-      <c r="AB29" s="122"/>
-      <c r="AC29" s="122"/>
-      <c r="AD29" s="122"/>
-      <c r="AE29" s="122"/>
-      <c r="AF29" s="122"/>
-      <c r="AG29" s="122"/>
-      <c r="AH29" s="122"/>
-      <c r="AI29" s="122"/>
-      <c r="AJ29" s="123"/>
-    </row>
-    <row r="30" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C30" s="132" t="s">
+      <c r="V29" s="85"/>
+      <c r="W29" s="85"/>
+      <c r="X29" s="85"/>
+      <c r="Y29" s="85"/>
+      <c r="Z29" s="85"/>
+      <c r="AA29" s="85"/>
+      <c r="AB29" s="85"/>
+      <c r="AC29" s="85"/>
+      <c r="AD29" s="85"/>
+      <c r="AE29" s="85"/>
+      <c r="AF29" s="85"/>
+      <c r="AG29" s="85"/>
+      <c r="AH29" s="85"/>
+      <c r="AI29" s="85"/>
+      <c r="AJ29" s="86"/>
+    </row>
+    <row r="30" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C30" s="95" t="s">
         <v>288</v>
       </c>
-      <c r="D30" s="125"/>
-      <c r="E30" s="125"/>
-      <c r="F30" s="125"/>
-      <c r="G30" s="125"/>
-      <c r="H30" s="125"/>
-      <c r="I30" s="125"/>
-      <c r="J30" s="125"/>
-      <c r="K30" s="125"/>
-      <c r="L30" s="125"/>
-      <c r="M30" s="125"/>
-      <c r="N30" s="125"/>
-      <c r="O30" s="125"/>
-      <c r="P30" s="125"/>
-      <c r="Q30" s="126"/>
-      <c r="U30" s="133" t="s">
+      <c r="D30" s="88"/>
+      <c r="E30" s="88"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="88"/>
+      <c r="I30" s="88"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="88"/>
+      <c r="L30" s="88"/>
+      <c r="M30" s="88"/>
+      <c r="N30" s="88"/>
+      <c r="O30" s="88"/>
+      <c r="P30" s="88"/>
+      <c r="Q30" s="89"/>
+      <c r="U30" s="96" t="s">
         <v>296</v>
       </c>
-      <c r="V30" s="125"/>
-      <c r="W30" s="125"/>
-      <c r="X30" s="125"/>
-      <c r="Y30" s="125"/>
-      <c r="Z30" s="125"/>
-      <c r="AA30" s="125"/>
-      <c r="AB30" s="125"/>
-      <c r="AC30" s="125"/>
-      <c r="AD30" s="125"/>
-      <c r="AE30" s="125"/>
-      <c r="AF30" s="125"/>
-      <c r="AG30" s="125"/>
-      <c r="AH30" s="125"/>
-      <c r="AI30" s="125"/>
-      <c r="AJ30" s="126"/>
-    </row>
-    <row r="31" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C31" s="132" t="s">
+      <c r="V30" s="88"/>
+      <c r="W30" s="88"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="88"/>
+      <c r="Z30" s="88"/>
+      <c r="AA30" s="88"/>
+      <c r="AB30" s="88"/>
+      <c r="AC30" s="88"/>
+      <c r="AD30" s="88"/>
+      <c r="AE30" s="88"/>
+      <c r="AF30" s="88"/>
+      <c r="AG30" s="88"/>
+      <c r="AH30" s="88"/>
+      <c r="AI30" s="88"/>
+      <c r="AJ30" s="89"/>
+    </row>
+    <row r="31" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C31" s="95" t="s">
         <v>289</v>
       </c>
-      <c r="D31" s="125"/>
-      <c r="E31" s="125"/>
-      <c r="F31" s="125"/>
-      <c r="G31" s="125"/>
-      <c r="H31" s="125"/>
-      <c r="I31" s="125"/>
-      <c r="J31" s="125"/>
-      <c r="K31" s="125"/>
-      <c r="L31" s="125"/>
-      <c r="M31" s="125"/>
-      <c r="N31" s="125"/>
-      <c r="O31" s="125"/>
-      <c r="P31" s="125"/>
-      <c r="Q31" s="126"/>
-      <c r="U31" s="135" t="s">
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
+      <c r="L31" s="88"/>
+      <c r="M31" s="88"/>
+      <c r="N31" s="88"/>
+      <c r="O31" s="88"/>
+      <c r="P31" s="88"/>
+      <c r="Q31" s="89"/>
+      <c r="U31" s="98" t="s">
         <v>297</v>
       </c>
-      <c r="V31" s="129"/>
-      <c r="W31" s="129"/>
-      <c r="X31" s="129"/>
-      <c r="Y31" s="129"/>
-      <c r="Z31" s="129"/>
-      <c r="AA31" s="129"/>
-      <c r="AB31" s="129"/>
-      <c r="AC31" s="129"/>
-      <c r="AD31" s="129"/>
-      <c r="AE31" s="129"/>
-      <c r="AF31" s="129"/>
-      <c r="AG31" s="129"/>
-      <c r="AH31" s="129"/>
-      <c r="AI31" s="129"/>
-      <c r="AJ31" s="130"/>
-    </row>
-    <row r="32" spans="1:63" ht="13.8" customHeight="1">
-      <c r="C32" s="133" t="s">
+      <c r="V31" s="92"/>
+      <c r="W31" s="92"/>
+      <c r="X31" s="92"/>
+      <c r="Y31" s="92"/>
+      <c r="Z31" s="92"/>
+      <c r="AA31" s="92"/>
+      <c r="AB31" s="92"/>
+      <c r="AC31" s="92"/>
+      <c r="AD31" s="92"/>
+      <c r="AE31" s="92"/>
+      <c r="AF31" s="92"/>
+      <c r="AG31" s="92"/>
+      <c r="AH31" s="92"/>
+      <c r="AI31" s="92"/>
+      <c r="AJ31" s="93"/>
+    </row>
+    <row r="32" spans="1:63" ht="13.9" customHeight="1">
+      <c r="C32" s="96" t="s">
         <v>290</v>
       </c>
-      <c r="D32" s="125"/>
-      <c r="E32" s="125"/>
-      <c r="F32" s="125"/>
-      <c r="G32" s="125"/>
-      <c r="H32" s="125"/>
-      <c r="I32" s="125"/>
-      <c r="J32" s="125"/>
-      <c r="K32" s="125"/>
-      <c r="L32" s="125"/>
-      <c r="M32" s="125"/>
-      <c r="N32" s="125"/>
-      <c r="O32" s="125"/>
-      <c r="P32" s="125"/>
-      <c r="Q32" s="126"/>
-    </row>
-    <row r="33" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C33" s="133"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="125"/>
-      <c r="G33" s="125"/>
-      <c r="H33" s="125"/>
-      <c r="I33" s="125"/>
-      <c r="J33" s="125"/>
-      <c r="K33" s="125"/>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125"/>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="126"/>
-    </row>
-    <row r="34" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C34" s="133" t="s">
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="88"/>
+      <c r="J32" s="88"/>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="M32" s="88"/>
+      <c r="N32" s="88"/>
+      <c r="O32" s="88"/>
+      <c r="P32" s="88"/>
+      <c r="Q32" s="89"/>
+    </row>
+    <row r="33" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C33" s="96"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="88"/>
+      <c r="K33" s="88"/>
+      <c r="L33" s="88"/>
+      <c r="M33" s="88"/>
+      <c r="N33" s="88"/>
+      <c r="O33" s="88"/>
+      <c r="P33" s="88"/>
+      <c r="Q33" s="89"/>
+    </row>
+    <row r="34" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C34" s="96" t="s">
         <v>291</v>
       </c>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="125"/>
-      <c r="G34" s="125"/>
-      <c r="H34" s="125"/>
-      <c r="I34" s="125"/>
-      <c r="J34" s="125"/>
-      <c r="K34" s="125"/>
-      <c r="L34" s="125"/>
-      <c r="M34" s="125"/>
-      <c r="N34" s="125"/>
-      <c r="O34" s="125"/>
-      <c r="P34" s="125"/>
-      <c r="Q34" s="126"/>
-    </row>
-    <row r="35" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C35" s="134" t="s">
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="88"/>
+      <c r="I34" s="88"/>
+      <c r="J34" s="88"/>
+      <c r="K34" s="88"/>
+      <c r="L34" s="88"/>
+      <c r="M34" s="88"/>
+      <c r="N34" s="88"/>
+      <c r="O34" s="88"/>
+      <c r="P34" s="88"/>
+      <c r="Q34" s="89"/>
+    </row>
+    <row r="35" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C35" s="97" t="s">
         <v>292</v>
       </c>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="125"/>
-      <c r="I35" s="125"/>
-      <c r="J35" s="125"/>
-      <c r="K35" s="125"/>
-      <c r="L35" s="125"/>
-      <c r="M35" s="125"/>
-      <c r="N35" s="125"/>
-      <c r="O35" s="125"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="126"/>
-    </row>
-    <row r="36" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C36" s="124" t="s">
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="88"/>
+      <c r="J35" s="88"/>
+      <c r="K35" s="88"/>
+      <c r="L35" s="88"/>
+      <c r="M35" s="88"/>
+      <c r="N35" s="88"/>
+      <c r="O35" s="88"/>
+      <c r="P35" s="88"/>
+      <c r="Q35" s="89"/>
+    </row>
+    <row r="36" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C36" s="87" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="125"/>
-      <c r="E36" s="125"/>
-      <c r="F36" s="125"/>
-      <c r="G36" s="125"/>
-      <c r="H36" s="125"/>
-      <c r="I36" s="125"/>
-      <c r="J36" s="125"/>
-      <c r="K36" s="125"/>
-      <c r="L36" s="125"/>
-      <c r="M36" s="125"/>
-      <c r="N36" s="125"/>
-      <c r="O36" s="125"/>
-      <c r="P36" s="125"/>
-      <c r="Q36" s="126"/>
-    </row>
-    <row r="37" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C37" s="133" t="s">
+      <c r="D36" s="88"/>
+      <c r="E36" s="88"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="88"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+      <c r="J36" s="88"/>
+      <c r="K36" s="88"/>
+      <c r="L36" s="88"/>
+      <c r="M36" s="88"/>
+      <c r="N36" s="88"/>
+      <c r="O36" s="88"/>
+      <c r="P36" s="88"/>
+      <c r="Q36" s="89"/>
+    </row>
+    <row r="37" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C37" s="96" t="s">
         <v>294</v>
       </c>
-      <c r="D37" s="125"/>
-      <c r="E37" s="125"/>
-      <c r="F37" s="125"/>
-      <c r="G37" s="125"/>
-      <c r="H37" s="125"/>
-      <c r="I37" s="125"/>
-      <c r="J37" s="125"/>
-      <c r="K37" s="125"/>
-      <c r="L37" s="125"/>
-      <c r="M37" s="125"/>
-      <c r="N37" s="125"/>
-      <c r="O37" s="125"/>
-      <c r="P37" s="125"/>
-      <c r="Q37" s="126"/>
-    </row>
-    <row r="38" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C38" s="135" t="s">
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="88"/>
+      <c r="M37" s="88"/>
+      <c r="N37" s="88"/>
+      <c r="O37" s="88"/>
+      <c r="P37" s="88"/>
+      <c r="Q37" s="89"/>
+    </row>
+    <row r="38" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C38" s="98" t="s">
         <v>239</v>
       </c>
-      <c r="D38" s="129"/>
-      <c r="E38" s="129"/>
-      <c r="F38" s="129"/>
-      <c r="G38" s="129"/>
-      <c r="H38" s="129"/>
-      <c r="I38" s="129"/>
-      <c r="J38" s="129"/>
-      <c r="K38" s="129"/>
-      <c r="L38" s="129"/>
-      <c r="M38" s="129"/>
-      <c r="N38" s="129"/>
-      <c r="O38" s="129"/>
-      <c r="P38" s="129"/>
-      <c r="Q38" s="130"/>
-    </row>
-    <row r="40" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C40" s="110"/>
-    </row>
-    <row r="42" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C42" s="115"/>
-      <c r="D42" s="115"/>
-    </row>
-    <row r="43" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C43" s="116"/>
-      <c r="D43" s="116"/>
-    </row>
-    <row r="44" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C44" s="116"/>
-      <c r="D44" s="116"/>
-    </row>
-    <row r="45" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C45" s="116"/>
-      <c r="D45" s="116"/>
-    </row>
-    <row r="46" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C46" s="116"/>
-      <c r="D46" s="116"/>
-    </row>
-    <row r="47" spans="3:17" ht="13.8" customHeight="1">
-      <c r="C47" s="116"/>
-      <c r="D47" s="116"/>
+      <c r="D38" s="92"/>
+      <c r="E38" s="92"/>
+      <c r="F38" s="92"/>
+      <c r="G38" s="92"/>
+      <c r="H38" s="92"/>
+      <c r="I38" s="92"/>
+      <c r="J38" s="92"/>
+      <c r="K38" s="92"/>
+      <c r="L38" s="92"/>
+      <c r="M38" s="92"/>
+      <c r="N38" s="92"/>
+      <c r="O38" s="92"/>
+      <c r="P38" s="92"/>
+      <c r="Q38" s="93"/>
+    </row>
+    <row r="40" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C40" s="73"/>
+    </row>
+    <row r="42" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C42" s="78"/>
+      <c r="D42" s="78"/>
+    </row>
+    <row r="43" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C43" s="79"/>
+      <c r="D43" s="79"/>
+    </row>
+    <row r="44" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C44" s="79"/>
+      <c r="D44" s="79"/>
+    </row>
+    <row r="45" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C45" s="79"/>
+      <c r="D45" s="79"/>
+    </row>
+    <row r="46" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C46" s="79"/>
+      <c r="D46" s="79"/>
+    </row>
+    <row r="47" spans="3:17" ht="13.9" customHeight="1">
+      <c r="C47" s="79"/>
+      <c r="D47" s="79"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8514,274 +8511,283 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:E63"/>
-  <sheetFormatPr defaultColWidth="2.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="3:5" ht="22.8">
-      <c r="C1" s="110" t="s">
+    <row r="1" spans="3:5" ht="23.25">
+      <c r="C1" s="73" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="2" spans="3:5">
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="74" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="3" spans="3:5">
-      <c r="C3" s="111" t="s">
+      <c r="C3" s="74" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="4" spans="3:5">
-      <c r="C4" s="111" t="s">
+      <c r="C4" s="74" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="5" spans="3:5">
-      <c r="C5" s="111" t="s">
+      <c r="C5" s="74" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="6" spans="3:5">
-      <c r="E6" s="112" t="s">
+      <c r="E6" s="75" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="7" spans="3:5">
-      <c r="E7" s="112" t="s">
+      <c r="E7" s="75" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="3:5" ht="22.8">
-      <c r="C9" s="110" t="s">
+    <row r="9" spans="3:5" ht="23.25">
+      <c r="C9" s="73" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="3:5" ht="17.399999999999999">
-      <c r="C10" s="113" t="s">
+    <row r="10" spans="3:5" ht="17.25">
+      <c r="C10" s="76" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="11" spans="3:5">
-      <c r="C11" s="111" t="s">
+      <c r="C11" s="74" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="12" spans="3:5">
-      <c r="C12" s="111" t="s">
+      <c r="C12" s="74" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="13" spans="3:5">
-      <c r="E13" s="112" t="s">
+      <c r="E13" s="75" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="14" spans="3:5">
-      <c r="E14" s="112" t="s">
+      <c r="E14" s="75" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="15" spans="3:5">
-      <c r="E15" s="112" t="s">
+      <c r="E15" s="75" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="16" spans="3:5">
-      <c r="E16" s="112" t="s">
+      <c r="E16" s="75" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="17" spans="3:5">
-      <c r="E17" s="112" t="s">
+      <c r="E17" s="75" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="18" spans="3:5">
-      <c r="E18" s="112" t="s">
+      <c r="E18" s="75" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="19" spans="3:5">
-      <c r="E19" s="112" t="s">
+      <c r="E19" s="75" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="20" spans="3:5">
-      <c r="E20" s="112" t="s">
+      <c r="E20" s="75" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="3:5">
-      <c r="E21" s="112" t="s">
+      <c r="E21" s="75" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="22" spans="3:5" ht="17.399999999999999">
-      <c r="C22" s="113" t="s">
+    <row r="22" spans="3:5" ht="17.25">
+      <c r="C22" s="76" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="23" spans="3:5">
-      <c r="E23" s="112" t="s">
+      <c r="E23" s="75" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="24" spans="3:5">
-      <c r="C24" s="112"/>
-    </row>
-    <row r="25" spans="3:5" ht="22.8">
-      <c r="C25" s="110" t="s">
+      <c r="C24" s="75"/>
+    </row>
+    <row r="25" spans="3:5" ht="23.25">
+      <c r="C25" s="73" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="26" spans="3:5" ht="17.399999999999999">
-      <c r="C26" s="113" t="s">
+    <row r="26" spans="3:5" ht="17.25">
+      <c r="C26" s="76" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="27" spans="3:5">
-      <c r="C27" s="111" t="s">
+      <c r="C27" s="74" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="28" spans="3:5">
-      <c r="D28" s="112" t="s">
+      <c r="D28" s="75" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="29" spans="3:5">
-      <c r="D29" s="112" t="s">
+      <c r="D29" s="75" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="30" spans="3:5">
-      <c r="D30" s="112" t="s">
+      <c r="D30" s="75" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="31" spans="3:5">
-      <c r="D31" s="112" t="s">
+      <c r="D31" s="75" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="33" spans="3:4" ht="17.399999999999999">
-      <c r="C33" s="113" t="s">
+    <row r="33" spans="3:4" ht="17.25">
+      <c r="C33" s="76" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="34" spans="3:4">
-      <c r="C34" s="111" t="s">
+      <c r="C34" s="74" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="35" spans="3:4">
-      <c r="D35" s="112" t="s">
+      <c r="D35" s="75" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="36" spans="3:4">
-      <c r="D36" s="112" t="s">
+      <c r="D36" s="75" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="37" spans="3:4">
-      <c r="D37" s="112" t="s">
+      <c r="D37" s="75" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="38" spans="3:4">
-      <c r="D38" s="112" t="s">
+      <c r="D38" s="75" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="40" spans="3:4" ht="22.8">
-      <c r="C40" s="110" t="s">
+    <row r="40" spans="3:4" ht="23.25">
+      <c r="C40" s="73" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="41" spans="3:4">
-      <c r="C41" s="111" t="s">
+      <c r="C41" s="74" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="42" spans="3:4">
-      <c r="C42" s="111" t="s">
+      <c r="C42" s="74" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="43" spans="3:4">
-      <c r="C43" s="114" t="s">
+      <c r="C43" s="77" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="44" spans="3:4">
-      <c r="C44" s="114" t="s">
+      <c r="C44" s="77" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="45" spans="3:4">
-      <c r="C45" s="114" t="s">
+      <c r="C45" s="77" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="46" spans="3:4">
-      <c r="C46" s="111"/>
+      <c r="C46" s="74"/>
     </row>
     <row r="47" spans="3:4">
-      <c r="C47" s="111" t="s">
+      <c r="C47" s="74" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="48" spans="3:4">
-      <c r="D48" s="112" t="s">
+      <c r="D48" s="75" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="49" spans="3:4">
-      <c r="D49" s="112" t="s">
+      <c r="D49" s="75" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="51" spans="3:4" ht="22.8">
-      <c r="C51" s="110" t="s">
+    <row r="51" spans="3:4" ht="23.25">
+      <c r="C51" s="73" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="52" spans="3:4">
-      <c r="C52" s="111" t="s">
+      <c r="C52" s="74" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="3:4" ht="22.8">
-      <c r="C56" s="110"/>
-    </row>
-    <row r="58" spans="3:4">
-      <c r="C58" s="115"/>
-      <c r="D58" s="115"/>
+    <row r="56" spans="3:4" ht="23.25">
+      <c r="C56" s="73"/>
+    </row>
+    <row r="58" spans="3:4" ht="15">
+      <c r="C58" s="78"/>
+      <c r="D58" s="78"/>
     </row>
     <row r="59" spans="3:4">
-      <c r="C59" s="116"/>
-      <c r="D59" s="116"/>
+      <c r="C59" s="79"/>
+      <c r="D59" s="79"/>
     </row>
     <row r="60" spans="3:4">
-      <c r="C60" s="116"/>
-      <c r="D60" s="116"/>
+      <c r="C60" s="79"/>
+      <c r="D60" s="79"/>
     </row>
     <row r="61" spans="3:4">
-      <c r="C61" s="116"/>
-      <c r="D61" s="116"/>
+      <c r="C61" s="79"/>
+      <c r="D61" s="79"/>
     </row>
     <row r="62" spans="3:4">
-      <c r="C62" s="116"/>
-      <c r="D62" s="116"/>
+      <c r="C62" s="79"/>
+      <c r="D62" s="79"/>
     </row>
     <row r="63" spans="3:4">
-      <c r="C63" s="116"/>
-      <c r="D63" s="116"/>
+      <c r="C63" s="79"/>
+      <c r="D63" s="79"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC47467-BEE9-4A44-8F61-D0BCCE72D6DF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>